--- a/data.xlsx
+++ b/data.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="18">
   <si>
     <t xml:space="preserve">السجل المدني </t>
   </si>
@@ -52,6 +52,24 @@
   </si>
   <si>
     <t>عبدالملك سالم اسعد رزق بدوي</t>
+  </si>
+  <si>
+    <t xml:space="preserve">المادة </t>
+  </si>
+  <si>
+    <t>الصف</t>
+  </si>
+  <si>
+    <t>الوحده</t>
+  </si>
+  <si>
+    <t>رياضيات</t>
+  </si>
+  <si>
+    <t>الثالث متوسط</t>
+  </si>
+  <si>
+    <t>الاولى</t>
   </si>
 </sst>
 </file>
@@ -390,13 +408,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="16.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -407,22 +425,31 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="H1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="I1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="J1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="K1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>111</v>
       </c>
@@ -432,24 +459,33 @@
       <c r="C2">
         <v>1</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2">
         <v>7</v>
       </c>
-      <c r="E2">
+      <c r="H2">
         <v>20</v>
       </c>
-      <c r="F2">
+      <c r="I2">
         <v>10</v>
       </c>
-      <c r="G2">
+      <c r="J2">
         <v>5</v>
       </c>
-      <c r="H2">
-        <f>SUM(D2:G2)</f>
+      <c r="K2">
+        <f>SUM(G2:J2)</f>
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>222</v>
       </c>
@@ -459,24 +495,33 @@
       <c r="C3">
         <v>2</v>
       </c>
-      <c r="D3">
+      <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3">
         <v>8</v>
       </c>
-      <c r="E3">
+      <c r="H3">
         <v>15</v>
       </c>
-      <c r="F3">
+      <c r="I3">
         <v>9</v>
       </c>
-      <c r="G3">
+      <c r="J3">
         <v>10</v>
       </c>
-      <c r="H3">
-        <f t="shared" ref="H3:H5" si="0">SUM(D3:G3)</f>
+      <c r="K3">
+        <f t="shared" ref="K3:K5" si="0">SUM(G3:J3)</f>
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>333</v>
       </c>
@@ -486,24 +531,33 @@
       <c r="C4">
         <v>3</v>
       </c>
-      <c r="D4">
+      <c r="D4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G4">
         <v>6</v>
       </c>
-      <c r="E4">
+      <c r="H4">
         <v>10</v>
       </c>
-      <c r="F4">
+      <c r="I4">
         <v>8</v>
       </c>
-      <c r="G4">
+      <c r="J4">
         <v>15</v>
       </c>
-      <c r="H4">
+      <c r="K4">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>444</v>
       </c>
@@ -513,19 +567,28 @@
       <c r="C5">
         <v>4</v>
       </c>
-      <c r="D5">
+      <c r="D5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5">
         <v>10</v>
       </c>
-      <c r="E5">
+      <c r="H5">
         <v>5</v>
       </c>
-      <c r="F5">
+      <c r="I5">
         <v>7</v>
       </c>
-      <c r="G5">
+      <c r="J5">
         <v>19</v>
       </c>
-      <c r="H5">
+      <c r="K5">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>

--- a/data.xlsx
+++ b/data.xlsx
@@ -1,22 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10731"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CF1FA681-7247-0A45-8CD1-4E9E02A59F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="ورقة1" sheetId="1" r:id="rId1"/>
-    <sheet name="ورقة2" sheetId="2" r:id="rId2"/>
-    <sheet name="ورقة3" sheetId="3" r:id="rId3"/>
+    <sheet name="الوحده الاولى" sheetId="1" r:id="rId1"/>
+    <sheet name="الوحده الثانيه" sheetId="2" r:id="rId2"/>
+    <sheet name="الوحده الثالثه" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="145621"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="20">
   <si>
     <t xml:space="preserve">السجل المدني </t>
   </si>
@@ -70,12 +84,18 @@
   </si>
   <si>
     <t>الاولى</t>
+  </si>
+  <si>
+    <t>الثالثه</t>
+  </si>
+  <si>
+    <t>الثانيه</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -109,7 +129,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="عادي" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -117,14 +137,17 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="نسق Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -162,7 +185,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -234,7 +257,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -407,14 +430,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K5"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="2" max="2" width="16.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.91796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -449,7 +472,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A2">
         <v>111</v>
       </c>
@@ -485,7 +508,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A3">
         <v>222</v>
       </c>
@@ -521,7 +544,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A4">
         <v>333</v>
       </c>
@@ -557,7 +580,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A5">
         <v>444</v>
       </c>
@@ -599,19 +622,385 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="2" max="2" width="16.91796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2">
+        <v>111</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2">
+        <v>7</v>
+      </c>
+      <c r="H2">
+        <v>20</v>
+      </c>
+      <c r="I2">
+        <v>10</v>
+      </c>
+      <c r="J2">
+        <v>5</v>
+      </c>
+      <c r="K2">
+        <f>SUM(G2:J2)</f>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A3">
+        <v>222</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3">
+        <v>8</v>
+      </c>
+      <c r="H3">
+        <v>15</v>
+      </c>
+      <c r="I3">
+        <v>9</v>
+      </c>
+      <c r="J3">
+        <v>10</v>
+      </c>
+      <c r="K3">
+        <f t="shared" ref="K3:K5" si="0">SUM(G3:J3)</f>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A4">
+        <v>333</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" t="s">
+        <v>19</v>
+      </c>
+      <c r="G4">
+        <v>6</v>
+      </c>
+      <c r="H4">
+        <v>10</v>
+      </c>
+      <c r="I4">
+        <v>8</v>
+      </c>
+      <c r="J4">
+        <v>15</v>
+      </c>
+      <c r="K4">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A5">
+        <v>444</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G5">
+        <v>10</v>
+      </c>
+      <c r="H5">
+        <v>5</v>
+      </c>
+      <c r="I5">
+        <v>7</v>
+      </c>
+      <c r="J5">
+        <v>19</v>
+      </c>
+      <c r="K5">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="2" max="2" width="16.91796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A2">
+        <v>111</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2">
+        <v>7</v>
+      </c>
+      <c r="H2">
+        <v>20</v>
+      </c>
+      <c r="I2">
+        <v>10</v>
+      </c>
+      <c r="J2">
+        <v>5</v>
+      </c>
+      <c r="K2">
+        <f>SUM(G2:J2)</f>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A3">
+        <v>222</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3">
+        <v>8</v>
+      </c>
+      <c r="H3">
+        <v>15</v>
+      </c>
+      <c r="I3">
+        <v>9</v>
+      </c>
+      <c r="J3">
+        <v>10</v>
+      </c>
+      <c r="K3">
+        <f t="shared" ref="K3:K5" si="0">SUM(G3:J3)</f>
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A4">
+        <v>333</v>
+      </c>
+      <c r="B4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4">
+        <v>6</v>
+      </c>
+      <c r="H4">
+        <v>10</v>
+      </c>
+      <c r="I4">
+        <v>8</v>
+      </c>
+      <c r="J4">
+        <v>15</v>
+      </c>
+      <c r="K4">
+        <f t="shared" si="0"/>
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.15">
+      <c r="A5">
+        <v>444</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5">
+        <v>10</v>
+      </c>
+      <c r="H5">
+        <v>5</v>
+      </c>
+      <c r="I5">
+        <v>7</v>
+      </c>
+      <c r="J5">
+        <v>19</v>
+      </c>
+      <c r="K5">
+        <f t="shared" si="0"/>
+        <v>41</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -5,7 +5,7 @@
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{CF1FA681-7247-0A45-8CD1-4E9E02A59F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="الوحده الاولى" sheetId="1" r:id="rId1"/>
@@ -492,20 +492,20 @@
         <v>17</v>
       </c>
       <c r="G2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H2">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="I2">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="J2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K2">
         <f>SUM(G2:J2)</f>
-        <v>42</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.15">
@@ -684,20 +684,20 @@
         <v>19</v>
       </c>
       <c r="G2">
+        <v>5</v>
+      </c>
+      <c r="H2">
+        <v>6</v>
+      </c>
+      <c r="I2">
         <v>7</v>
       </c>
-      <c r="H2">
-        <v>20</v>
-      </c>
-      <c r="I2">
-        <v>10</v>
-      </c>
       <c r="J2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K2">
         <f>SUM(G2:J2)</f>
-        <v>42</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.15">
@@ -876,20 +876,20 @@
         <v>18</v>
       </c>
       <c r="G2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="H2">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="I2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J2">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="K2">
         <f>SUM(G2:J2)</f>
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.15">

--- a/data.xlsx
+++ b/data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10731"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CF1FA681-7247-0A45-8CD1-4E9E02A59F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4B4916BC-A911-5E4D-94C5-2377CA130C1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -30,10 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="20">
-  <si>
-    <t xml:space="preserve">السجل المدني </t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="21">
   <si>
     <t>اسم الطالب</t>
   </si>
@@ -90,6 +87,9 @@
   </si>
   <si>
     <t>الثانيه</t>
+  </si>
+  <si>
+    <t xml:space="preserve">رقم الطالب </t>
   </si>
 </sst>
 </file>
@@ -439,37 +439,37 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>3</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>4</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>5</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>6</v>
-      </c>
-      <c r="K1" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.15">
@@ -477,35 +477,35 @@
         <v>111</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" t="s">
         <v>16</v>
       </c>
-      <c r="F2" t="s">
-        <v>17</v>
-      </c>
       <c r="G2">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H2">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="I2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="J2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K2">
         <f>SUM(G2:J2)</f>
-        <v>10</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.15">
@@ -513,19 +513,19 @@
         <v>222</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" t="s">
         <v>16</v>
-      </c>
-      <c r="F3" t="s">
-        <v>17</v>
       </c>
       <c r="G3">
         <v>8</v>
@@ -549,19 +549,19 @@
         <v>333</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C4">
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E4" t="s">
+        <v>15</v>
+      </c>
+      <c r="F4" t="s">
         <v>16</v>
-      </c>
-      <c r="F4" t="s">
-        <v>17</v>
       </c>
       <c r="G4">
         <v>6</v>
@@ -585,19 +585,19 @@
         <v>444</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C5">
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" t="s">
         <v>16</v>
-      </c>
-      <c r="F5" t="s">
-        <v>17</v>
       </c>
       <c r="G5">
         <v>10</v>
@@ -631,37 +631,37 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>3</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>4</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>5</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>6</v>
-      </c>
-      <c r="K1" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.15">
@@ -669,35 +669,35 @@
         <v>111</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G2">
+        <v>7</v>
+      </c>
+      <c r="H2">
+        <v>20</v>
+      </c>
+      <c r="I2">
+        <v>10</v>
+      </c>
+      <c r="J2">
         <v>5</v>
-      </c>
-      <c r="H2">
-        <v>6</v>
-      </c>
-      <c r="I2">
-        <v>7</v>
-      </c>
-      <c r="J2">
-        <v>8</v>
       </c>
       <c r="K2">
         <f>SUM(G2:J2)</f>
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.15">
@@ -705,19 +705,19 @@
         <v>222</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G3">
         <v>8</v>
@@ -741,19 +741,19 @@
         <v>333</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C4">
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G4">
         <v>6</v>
@@ -777,19 +777,19 @@
         <v>444</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C5">
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G5">
         <v>10</v>
@@ -823,37 +823,37 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>3</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>4</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>5</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>6</v>
-      </c>
-      <c r="K1" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.15">
@@ -861,35 +861,35 @@
         <v>111</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H2">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="I2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J2">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="K2">
         <f>SUM(G2:J2)</f>
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.15">
@@ -897,19 +897,19 @@
         <v>222</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C3">
         <v>2</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G3">
         <v>8</v>
@@ -933,19 +933,19 @@
         <v>333</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C4">
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G4">
         <v>6</v>
@@ -969,19 +969,19 @@
         <v>444</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C5">
         <v>4</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G5">
         <v>10</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U102"/>
+  <dimension ref="A1:U105"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -414,7 +414,7 @@
         <v>الفصل</v>
       </c>
       <c r="D1" t="str">
-        <v>واجب درس 11</v>
+        <v>واجب درس 1</v>
       </c>
       <c r="E1" t="str">
         <v>واجب درس 2</v>
@@ -432,7 +432,7 @@
         <v>واجب درس 6</v>
       </c>
       <c r="J1" t="str">
-        <v>نشاط درس 11</v>
+        <v>نشاط درس 1</v>
       </c>
       <c r="K1" t="str">
         <v>نشاط درس 2</v>
@@ -487,14 +487,14 @@
       <c r="F2">
         <v>10</v>
       </c>
-      <c r="G2">
-        <v>10</v>
-      </c>
-      <c r="H2">
-        <v>10</v>
-      </c>
-      <c r="I2">
-        <v>10</v>
+      <c r="G2" t="str">
+        <v>8</v>
+      </c>
+      <c r="H2" t="str">
+        <v>8</v>
+      </c>
+      <c r="I2" t="str">
+        <v>8</v>
       </c>
       <c r="J2">
         <v>20</v>
@@ -505,32 +505,32 @@
       <c r="L2">
         <v>20</v>
       </c>
-      <c r="M2">
+      <c r="M2" t="str">
+        <v>10</v>
+      </c>
+      <c r="N2" t="str">
+        <v>10</v>
+      </c>
+      <c r="O2" t="str">
+        <v>10</v>
+      </c>
+      <c r="P2" t="str">
+        <v>4.00</v>
+      </c>
+      <c r="Q2" t="str">
+        <v>15</v>
+      </c>
+      <c r="R2" t="str">
         <v>20</v>
       </c>
-      <c r="N2">
-        <v>20</v>
-      </c>
-      <c r="O2">
-        <v>20</v>
-      </c>
-      <c r="P2" t="str">
-        <v>6.00</v>
-      </c>
-      <c r="Q2">
-        <v>10</v>
-      </c>
-      <c r="R2">
-        <v>19</v>
-      </c>
       <c r="S2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="T2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U2">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -580,7 +580,7 @@
         <v>20</v>
       </c>
       <c r="P3" t="str">
-        <v>9.50</v>
+        <v>9.00</v>
       </c>
       <c r="Q3">
         <v>14</v>
@@ -592,7 +592,7 @@
         <v>0</v>
       </c>
       <c r="T3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U3">
         <v>0</v>
@@ -645,7 +645,7 @@
         <v>20</v>
       </c>
       <c r="P4" t="str">
-        <v>10.00</v>
+        <v>9.50</v>
       </c>
       <c r="Q4">
         <v>14</v>
@@ -660,7 +660,7 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -710,16 +710,16 @@
         <v>20</v>
       </c>
       <c r="P5" t="str">
-        <v>10.00</v>
+        <v>9.50</v>
       </c>
       <c r="Q5">
         <v>13</v>
       </c>
-      <c r="R5">
+      <c r="R5" t="str">
+        <v>0</v>
+      </c>
+      <c r="S5">
         <v>1</v>
-      </c>
-      <c r="S5">
-        <v>0</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -775,7 +775,7 @@
         <v>20</v>
       </c>
       <c r="P6" t="str">
-        <v>10.00</v>
+        <v>9.50</v>
       </c>
       <c r="Q6">
         <v>3</v>
@@ -787,7 +787,7 @@
         <v>0</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U6">
         <v>0</v>
@@ -905,7 +905,7 @@
         <v>20</v>
       </c>
       <c r="P8" t="str">
-        <v>10.00</v>
+        <v>9.50</v>
       </c>
       <c r="Q8">
         <v>16</v>
@@ -914,7 +914,7 @@
         <v>12</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T8">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>20</v>
       </c>
       <c r="P10" t="str">
-        <v>10.00</v>
+        <v>9.00</v>
       </c>
       <c r="Q10">
         <v>19</v>
@@ -1050,7 +1050,7 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1149,8 +1149,8 @@
       <c r="J12">
         <v>20</v>
       </c>
-      <c r="K12">
-        <v>20</v>
+      <c r="K12" t="str">
+        <v>10</v>
       </c>
       <c r="L12">
         <v>20</v>
@@ -1230,7 +1230,7 @@
         <v>9</v>
       </c>
       <c r="P13" t="str">
-        <v>9.00</v>
+        <v>8.00</v>
       </c>
       <c r="Q13">
         <v>9</v>
@@ -1245,7 +1245,7 @@
         <v>1</v>
       </c>
       <c r="U13">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -1750,7 +1750,7 @@
         <v>20</v>
       </c>
       <c r="P21" t="str">
-        <v>10.00</v>
+        <v>9.50</v>
       </c>
       <c r="Q21">
         <v>13</v>
@@ -1759,7 +1759,7 @@
         <v>18</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T21">
         <v>0</v>
@@ -1815,7 +1815,7 @@
         <v>20</v>
       </c>
       <c r="P22" t="str">
-        <v>10.00</v>
+        <v>9.50</v>
       </c>
       <c r="Q22">
         <v>7</v>
@@ -1830,7 +1830,7 @@
         <v>0</v>
       </c>
       <c r="U22">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -6105,7 +6105,7 @@
         <v>20</v>
       </c>
       <c r="P88" t="str">
-        <v>10.00</v>
+        <v>9.00</v>
       </c>
       <c r="Q88">
         <v>19</v>
@@ -6117,10 +6117,10 @@
         <v>0</v>
       </c>
       <c r="T88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U88">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
@@ -6905,10 +6905,10 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>34387</v>
+        <v>22323</v>
       </c>
       <c r="B101" t="str">
-        <v>عمر عبدالرحمن بن يحيى سيدي بابا</v>
+        <v>عمر</v>
       </c>
       <c r="C101" t="str">
         <v>ثالث 2</v>
@@ -6970,79 +6970,274 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
+        <v>34387</v>
+      </c>
+      <c r="B102" t="str">
+        <v>عمر عبدالرحمن بن يحيى سيدي بابا</v>
+      </c>
+      <c r="C102" t="str">
+        <v>ثالث 2</v>
+      </c>
+      <c r="D102" t="str">
+        <v/>
+      </c>
+      <c r="E102" t="str">
+        <v/>
+      </c>
+      <c r="F102" t="str">
+        <v/>
+      </c>
+      <c r="G102" t="str">
+        <v/>
+      </c>
+      <c r="H102" t="str">
+        <v/>
+      </c>
+      <c r="I102" t="str">
+        <v/>
+      </c>
+      <c r="J102" t="str">
+        <v/>
+      </c>
+      <c r="K102" t="str">
+        <v/>
+      </c>
+      <c r="L102" t="str">
+        <v/>
+      </c>
+      <c r="M102" t="str">
+        <v/>
+      </c>
+      <c r="N102" t="str">
+        <v/>
+      </c>
+      <c r="O102" t="str">
+        <v/>
+      </c>
+      <c r="P102" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="Q102" t="str">
+        <v/>
+      </c>
+      <c r="R102" t="str">
+        <v/>
+      </c>
+      <c r="S102">
+        <v>0</v>
+      </c>
+      <c r="T102">
+        <v>0</v>
+      </c>
+      <c r="U102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>11111</v>
+      </c>
+      <c r="B103" t="str">
+        <v>عمران</v>
+      </c>
+      <c r="C103" t="str">
+        <v>ثالث 1</v>
+      </c>
+      <c r="D103" t="str">
+        <v/>
+      </c>
+      <c r="E103" t="str">
+        <v/>
+      </c>
+      <c r="F103" t="str">
+        <v/>
+      </c>
+      <c r="G103" t="str">
+        <v/>
+      </c>
+      <c r="H103" t="str">
+        <v/>
+      </c>
+      <c r="I103" t="str">
+        <v/>
+      </c>
+      <c r="J103" t="str">
+        <v/>
+      </c>
+      <c r="K103" t="str">
+        <v/>
+      </c>
+      <c r="L103" t="str">
+        <v/>
+      </c>
+      <c r="M103" t="str">
+        <v/>
+      </c>
+      <c r="N103" t="str">
+        <v/>
+      </c>
+      <c r="O103" t="str">
+        <v/>
+      </c>
+      <c r="P103" t="str">
+        <v>9.50</v>
+      </c>
+      <c r="Q103" t="str">
+        <v/>
+      </c>
+      <c r="R103" t="str">
+        <v/>
+      </c>
+      <c r="S103">
+        <v>0</v>
+      </c>
+      <c r="T103">
+        <v>1</v>
+      </c>
+      <c r="U103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>22222</v>
+      </c>
+      <c r="B104" t="str">
+        <v>لوى</v>
+      </c>
+      <c r="C104" t="str">
+        <v>ثالث 1</v>
+      </c>
+      <c r="D104" t="str">
+        <v/>
+      </c>
+      <c r="E104" t="str">
+        <v/>
+      </c>
+      <c r="F104" t="str">
+        <v/>
+      </c>
+      <c r="G104" t="str">
+        <v/>
+      </c>
+      <c r="H104" t="str">
+        <v/>
+      </c>
+      <c r="I104" t="str">
+        <v/>
+      </c>
+      <c r="J104" t="str">
+        <v/>
+      </c>
+      <c r="K104" t="str">
+        <v/>
+      </c>
+      <c r="L104" t="str">
+        <v/>
+      </c>
+      <c r="M104" t="str">
+        <v/>
+      </c>
+      <c r="N104" t="str">
+        <v/>
+      </c>
+      <c r="O104" t="str">
+        <v/>
+      </c>
+      <c r="P104" t="str">
+        <v>9.50</v>
+      </c>
+      <c r="Q104" t="str">
+        <v/>
+      </c>
+      <c r="R104" t="str">
+        <v/>
+      </c>
+      <c r="S104">
+        <v>1</v>
+      </c>
+      <c r="T104">
+        <v>0</v>
+      </c>
+      <c r="U104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
         <v>55201</v>
       </c>
-      <c r="B102" t="str">
+      <c r="B105" t="str">
         <v>محمد حمزة محمود سليمان</v>
       </c>
-      <c r="C102" t="str">
+      <c r="C105" t="str">
         <v>ثالث 1</v>
       </c>
-      <c r="D102">
+      <c r="D105">
         <v>10</v>
       </c>
-      <c r="E102">
+      <c r="E105">
         <v>10</v>
       </c>
-      <c r="F102">
+      <c r="F105">
         <v>10</v>
       </c>
-      <c r="G102">
+      <c r="G105">
         <v>10</v>
       </c>
-      <c r="H102">
+      <c r="H105">
         <v>10</v>
       </c>
-      <c r="I102">
+      <c r="I105">
         <v>10</v>
       </c>
-      <c r="J102">
+      <c r="J105">
         <v>20</v>
       </c>
-      <c r="K102">
+      <c r="K105">
         <v>20</v>
       </c>
-      <c r="L102">
+      <c r="L105">
         <v>20</v>
       </c>
-      <c r="M102">
+      <c r="M105">
         <v>20</v>
       </c>
-      <c r="N102">
+      <c r="N105">
         <v>20</v>
       </c>
-      <c r="O102">
+      <c r="O105">
         <v>20</v>
       </c>
-      <c r="P102" t="str">
-        <v>10.00</v>
-      </c>
-      <c r="Q102">
+      <c r="P105" t="str">
+        <v>9.50</v>
+      </c>
+      <c r="Q105">
         <v>4</v>
       </c>
-      <c r="R102">
+      <c r="R105">
         <v>12</v>
       </c>
-      <c r="S102">
-        <v>0</v>
-      </c>
-      <c r="T102">
-        <v>0</v>
-      </c>
-      <c r="U102">
+      <c r="S105">
+        <v>1</v>
+      </c>
+      <c r="T105">
+        <v>0</v>
+      </c>
+      <c r="U105">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:U102"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:U105"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O102"/>
+  <dimension ref="A1:O105"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -7102,40 +7297,40 @@
         <v>ثالث 1</v>
       </c>
       <c r="D2" t="str">
-        <v/>
+        <v>10</v>
       </c>
       <c r="E2" t="str">
-        <v/>
+        <v>9</v>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>8</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>11</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>12</v>
       </c>
       <c r="I2" t="str">
-        <v/>
+        <v>13</v>
       </c>
       <c r="J2" t="str">
-        <v>6.00</v>
+        <v>4.00</v>
       </c>
       <c r="K2" t="str">
-        <v/>
+        <v>18</v>
       </c>
       <c r="L2" t="str">
-        <v/>
+        <v>20</v>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O2">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -7167,7 +7362,7 @@
         <v/>
       </c>
       <c r="J3" t="str">
-        <v>9.50</v>
+        <v>9.00</v>
       </c>
       <c r="K3" t="str">
         <v/>
@@ -7179,7 +7374,7 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O3">
         <v>0</v>
@@ -7214,7 +7409,7 @@
         <v/>
       </c>
       <c r="J4" t="str">
-        <v>10.00</v>
+        <v>9.50</v>
       </c>
       <c r="K4" t="str">
         <v/>
@@ -7229,7 +7424,7 @@
         <v>0</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -7261,7 +7456,7 @@
         <v/>
       </c>
       <c r="J5" t="str">
-        <v>10.00</v>
+        <v>9.50</v>
       </c>
       <c r="K5" t="str">
         <v/>
@@ -7270,7 +7465,7 @@
         <v/>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5">
         <v>0</v>
@@ -7308,7 +7503,7 @@
         <v/>
       </c>
       <c r="J6" t="str">
-        <v>10.00</v>
+        <v>9.50</v>
       </c>
       <c r="K6" t="str">
         <v/>
@@ -7320,7 +7515,7 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -7402,7 +7597,7 @@
         <v/>
       </c>
       <c r="J8" t="str">
-        <v>10.00</v>
+        <v>9.50</v>
       </c>
       <c r="K8" t="str">
         <v/>
@@ -7411,7 +7606,7 @@
         <v/>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -7496,7 +7691,7 @@
         <v/>
       </c>
       <c r="J10" t="str">
-        <v>10.00</v>
+        <v>9.00</v>
       </c>
       <c r="K10" t="str">
         <v/>
@@ -7511,7 +7706,7 @@
         <v>0</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -7637,7 +7832,7 @@
         <v>3</v>
       </c>
       <c r="J13" t="str">
-        <v>9.00</v>
+        <v>8.00</v>
       </c>
       <c r="K13" t="str">
         <v>9</v>
@@ -7652,7 +7847,7 @@
         <v>1</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -8013,7 +8208,7 @@
         <v/>
       </c>
       <c r="J21" t="str">
-        <v>10.00</v>
+        <v>9.50</v>
       </c>
       <c r="K21" t="str">
         <v/>
@@ -8022,7 +8217,7 @@
         <v/>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N21">
         <v>0</v>
@@ -8060,7 +8255,7 @@
         <v/>
       </c>
       <c r="J22" t="str">
-        <v>10.00</v>
+        <v>9.50</v>
       </c>
       <c r="K22" t="str">
         <v/>
@@ -8075,7 +8270,7 @@
         <v>0</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -11162,7 +11357,7 @@
         <v/>
       </c>
       <c r="J88" t="str">
-        <v>10.00</v>
+        <v>9.00</v>
       </c>
       <c r="K88" t="str">
         <v/>
@@ -11174,10 +11369,10 @@
         <v>0</v>
       </c>
       <c r="N88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O88">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
@@ -11746,10 +11941,10 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>34387</v>
+        <v>22323</v>
       </c>
       <c r="B101" t="str">
-        <v>عمر عبدالرحمن بن يحيى سيدي بابا</v>
+        <v>عمر</v>
       </c>
       <c r="C101" t="str">
         <v>ثالث 2</v>
@@ -11793,61 +11988,202 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
+        <v>34387</v>
+      </c>
+      <c r="B102" t="str">
+        <v>عمر عبدالرحمن بن يحيى سيدي بابا</v>
+      </c>
+      <c r="C102" t="str">
+        <v>ثالث 2</v>
+      </c>
+      <c r="D102" t="str">
+        <v/>
+      </c>
+      <c r="E102" t="str">
+        <v/>
+      </c>
+      <c r="F102" t="str">
+        <v/>
+      </c>
+      <c r="G102" t="str">
+        <v/>
+      </c>
+      <c r="H102" t="str">
+        <v/>
+      </c>
+      <c r="I102" t="str">
+        <v/>
+      </c>
+      <c r="J102" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="K102" t="str">
+        <v/>
+      </c>
+      <c r="L102" t="str">
+        <v/>
+      </c>
+      <c r="M102">
+        <v>0</v>
+      </c>
+      <c r="N102">
+        <v>0</v>
+      </c>
+      <c r="O102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>11111</v>
+      </c>
+      <c r="B103" t="str">
+        <v>عمران</v>
+      </c>
+      <c r="C103" t="str">
+        <v>ثالث 1</v>
+      </c>
+      <c r="D103" t="str">
+        <v/>
+      </c>
+      <c r="E103" t="str">
+        <v/>
+      </c>
+      <c r="F103" t="str">
+        <v/>
+      </c>
+      <c r="G103" t="str">
+        <v/>
+      </c>
+      <c r="H103" t="str">
+        <v/>
+      </c>
+      <c r="I103" t="str">
+        <v/>
+      </c>
+      <c r="J103" t="str">
+        <v>9.50</v>
+      </c>
+      <c r="K103" t="str">
+        <v/>
+      </c>
+      <c r="L103" t="str">
+        <v/>
+      </c>
+      <c r="M103">
+        <v>0</v>
+      </c>
+      <c r="N103">
+        <v>1</v>
+      </c>
+      <c r="O103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>22222</v>
+      </c>
+      <c r="B104" t="str">
+        <v>لوى</v>
+      </c>
+      <c r="C104" t="str">
+        <v>ثالث 1</v>
+      </c>
+      <c r="D104" t="str">
+        <v/>
+      </c>
+      <c r="E104" t="str">
+        <v/>
+      </c>
+      <c r="F104" t="str">
+        <v/>
+      </c>
+      <c r="G104" t="str">
+        <v/>
+      </c>
+      <c r="H104" t="str">
+        <v/>
+      </c>
+      <c r="I104" t="str">
+        <v/>
+      </c>
+      <c r="J104" t="str">
+        <v>9.50</v>
+      </c>
+      <c r="K104" t="str">
+        <v/>
+      </c>
+      <c r="L104" t="str">
+        <v/>
+      </c>
+      <c r="M104">
+        <v>1</v>
+      </c>
+      <c r="N104">
+        <v>0</v>
+      </c>
+      <c r="O104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
         <v>55201</v>
       </c>
-      <c r="B102" t="str">
+      <c r="B105" t="str">
         <v>محمد حمزة محمود سليمان</v>
       </c>
-      <c r="C102" t="str">
+      <c r="C105" t="str">
         <v>ثالث 1</v>
       </c>
-      <c r="D102" t="str">
-        <v/>
-      </c>
-      <c r="E102" t="str">
-        <v/>
-      </c>
-      <c r="F102" t="str">
-        <v/>
-      </c>
-      <c r="G102" t="str">
-        <v/>
-      </c>
-      <c r="H102" t="str">
-        <v/>
-      </c>
-      <c r="I102" t="str">
-        <v/>
-      </c>
-      <c r="J102" t="str">
-        <v>10.00</v>
-      </c>
-      <c r="K102" t="str">
-        <v/>
-      </c>
-      <c r="L102" t="str">
-        <v/>
-      </c>
-      <c r="M102">
-        <v>0</v>
-      </c>
-      <c r="N102">
-        <v>0</v>
-      </c>
-      <c r="O102">
+      <c r="D105" t="str">
+        <v/>
+      </c>
+      <c r="E105" t="str">
+        <v/>
+      </c>
+      <c r="F105" t="str">
+        <v/>
+      </c>
+      <c r="G105" t="str">
+        <v/>
+      </c>
+      <c r="H105" t="str">
+        <v/>
+      </c>
+      <c r="I105" t="str">
+        <v/>
+      </c>
+      <c r="J105" t="str">
+        <v>9.50</v>
+      </c>
+      <c r="K105" t="str">
+        <v/>
+      </c>
+      <c r="L105" t="str">
+        <v/>
+      </c>
+      <c r="M105">
+        <v>1</v>
+      </c>
+      <c r="N105">
+        <v>0</v>
+      </c>
+      <c r="O105">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O102"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O105"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O102"/>
+  <dimension ref="A1:O105"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -11925,7 +12261,7 @@
         <v/>
       </c>
       <c r="J2" t="str">
-        <v>6.00</v>
+        <v>4.00</v>
       </c>
       <c r="K2" t="str">
         <v/>
@@ -11934,13 +12270,13 @@
         <v/>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O2">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -11972,7 +12308,7 @@
         <v/>
       </c>
       <c r="J3" t="str">
-        <v>9.50</v>
+        <v>9.00</v>
       </c>
       <c r="K3" t="str">
         <v/>
@@ -11984,7 +12320,7 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O3">
         <v>0</v>
@@ -12019,7 +12355,7 @@
         <v/>
       </c>
       <c r="J4" t="str">
-        <v>10.00</v>
+        <v>9.50</v>
       </c>
       <c r="K4" t="str">
         <v/>
@@ -12034,7 +12370,7 @@
         <v>0</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -12066,7 +12402,7 @@
         <v/>
       </c>
       <c r="J5" t="str">
-        <v>10.00</v>
+        <v>9.50</v>
       </c>
       <c r="K5" t="str">
         <v/>
@@ -12075,7 +12411,7 @@
         <v/>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5">
         <v>0</v>
@@ -12113,7 +12449,7 @@
         <v/>
       </c>
       <c r="J6" t="str">
-        <v>10.00</v>
+        <v>9.50</v>
       </c>
       <c r="K6" t="str">
         <v/>
@@ -12125,7 +12461,7 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -12207,7 +12543,7 @@
         <v/>
       </c>
       <c r="J8" t="str">
-        <v>10.00</v>
+        <v>9.50</v>
       </c>
       <c r="K8" t="str">
         <v/>
@@ -12216,7 +12552,7 @@
         <v/>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -12301,7 +12637,7 @@
         <v/>
       </c>
       <c r="J10" t="str">
-        <v>10.00</v>
+        <v>9.00</v>
       </c>
       <c r="K10" t="str">
         <v/>
@@ -12316,7 +12652,7 @@
         <v>0</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -12442,7 +12778,7 @@
         <v>4</v>
       </c>
       <c r="J13" t="str">
-        <v>9.00</v>
+        <v>8.00</v>
       </c>
       <c r="K13" t="str">
         <v>20</v>
@@ -12457,7 +12793,7 @@
         <v>1</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -12818,7 +13154,7 @@
         <v/>
       </c>
       <c r="J21" t="str">
-        <v>10.00</v>
+        <v>9.50</v>
       </c>
       <c r="K21" t="str">
         <v/>
@@ -12827,7 +13163,7 @@
         <v/>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N21">
         <v>0</v>
@@ -12865,7 +13201,7 @@
         <v/>
       </c>
       <c r="J22" t="str">
-        <v>10.00</v>
+        <v>9.50</v>
       </c>
       <c r="K22" t="str">
         <v/>
@@ -12880,7 +13216,7 @@
         <v>0</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -15967,7 +16303,7 @@
         <v/>
       </c>
       <c r="J88" t="str">
-        <v>10.00</v>
+        <v>9.00</v>
       </c>
       <c r="K88" t="str">
         <v/>
@@ -15979,10 +16315,10 @@
         <v>0</v>
       </c>
       <c r="N88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O88">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
@@ -16551,10 +16887,10 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>34387</v>
+        <v>22323</v>
       </c>
       <c r="B101" t="str">
-        <v>عمر عبدالرحمن بن يحيى سيدي بابا</v>
+        <v>عمر</v>
       </c>
       <c r="C101" t="str">
         <v>ثالث 2</v>
@@ -16598,61 +16934,202 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
+        <v>34387</v>
+      </c>
+      <c r="B102" t="str">
+        <v>عمر عبدالرحمن بن يحيى سيدي بابا</v>
+      </c>
+      <c r="C102" t="str">
+        <v>ثالث 2</v>
+      </c>
+      <c r="D102" t="str">
+        <v/>
+      </c>
+      <c r="E102" t="str">
+        <v/>
+      </c>
+      <c r="F102" t="str">
+        <v/>
+      </c>
+      <c r="G102" t="str">
+        <v/>
+      </c>
+      <c r="H102" t="str">
+        <v/>
+      </c>
+      <c r="I102" t="str">
+        <v/>
+      </c>
+      <c r="J102" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="K102" t="str">
+        <v/>
+      </c>
+      <c r="L102" t="str">
+        <v/>
+      </c>
+      <c r="M102">
+        <v>0</v>
+      </c>
+      <c r="N102">
+        <v>0</v>
+      </c>
+      <c r="O102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>11111</v>
+      </c>
+      <c r="B103" t="str">
+        <v>عمران</v>
+      </c>
+      <c r="C103" t="str">
+        <v>ثالث 1</v>
+      </c>
+      <c r="D103" t="str">
+        <v/>
+      </c>
+      <c r="E103" t="str">
+        <v/>
+      </c>
+      <c r="F103" t="str">
+        <v/>
+      </c>
+      <c r="G103" t="str">
+        <v/>
+      </c>
+      <c r="H103" t="str">
+        <v/>
+      </c>
+      <c r="I103" t="str">
+        <v/>
+      </c>
+      <c r="J103" t="str">
+        <v>9.50</v>
+      </c>
+      <c r="K103" t="str">
+        <v/>
+      </c>
+      <c r="L103" t="str">
+        <v/>
+      </c>
+      <c r="M103">
+        <v>0</v>
+      </c>
+      <c r="N103">
+        <v>1</v>
+      </c>
+      <c r="O103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>22222</v>
+      </c>
+      <c r="B104" t="str">
+        <v>لوى</v>
+      </c>
+      <c r="C104" t="str">
+        <v>ثالث 1</v>
+      </c>
+      <c r="D104" t="str">
+        <v/>
+      </c>
+      <c r="E104" t="str">
+        <v/>
+      </c>
+      <c r="F104" t="str">
+        <v/>
+      </c>
+      <c r="G104" t="str">
+        <v/>
+      </c>
+      <c r="H104" t="str">
+        <v/>
+      </c>
+      <c r="I104" t="str">
+        <v/>
+      </c>
+      <c r="J104" t="str">
+        <v>9.50</v>
+      </c>
+      <c r="K104" t="str">
+        <v/>
+      </c>
+      <c r="L104" t="str">
+        <v/>
+      </c>
+      <c r="M104">
+        <v>1</v>
+      </c>
+      <c r="N104">
+        <v>0</v>
+      </c>
+      <c r="O104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
         <v>55201</v>
       </c>
-      <c r="B102" t="str">
+      <c r="B105" t="str">
         <v>محمد حمزة محمود سليمان</v>
       </c>
-      <c r="C102" t="str">
+      <c r="C105" t="str">
         <v>ثالث 1</v>
       </c>
-      <c r="D102" t="str">
-        <v/>
-      </c>
-      <c r="E102" t="str">
-        <v/>
-      </c>
-      <c r="F102" t="str">
-        <v/>
-      </c>
-      <c r="G102" t="str">
-        <v/>
-      </c>
-      <c r="H102" t="str">
-        <v/>
-      </c>
-      <c r="I102" t="str">
-        <v/>
-      </c>
-      <c r="J102" t="str">
-        <v>10.00</v>
-      </c>
-      <c r="K102" t="str">
-        <v/>
-      </c>
-      <c r="L102" t="str">
-        <v/>
-      </c>
-      <c r="M102">
-        <v>0</v>
-      </c>
-      <c r="N102">
-        <v>0</v>
-      </c>
-      <c r="O102">
+      <c r="D105" t="str">
+        <v/>
+      </c>
+      <c r="E105" t="str">
+        <v/>
+      </c>
+      <c r="F105" t="str">
+        <v/>
+      </c>
+      <c r="G105" t="str">
+        <v/>
+      </c>
+      <c r="H105" t="str">
+        <v/>
+      </c>
+      <c r="I105" t="str">
+        <v/>
+      </c>
+      <c r="J105" t="str">
+        <v>9.50</v>
+      </c>
+      <c r="K105" t="str">
+        <v/>
+      </c>
+      <c r="L105" t="str">
+        <v/>
+      </c>
+      <c r="M105">
+        <v>1</v>
+      </c>
+      <c r="N105">
+        <v>0</v>
+      </c>
+      <c r="O105">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O102"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O105"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O102"/>
+  <dimension ref="A1:O105"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -16730,7 +17207,7 @@
         <v/>
       </c>
       <c r="J2" t="str">
-        <v>6.00</v>
+        <v>4.00</v>
       </c>
       <c r="K2" t="str">
         <v/>
@@ -16739,13 +17216,13 @@
         <v/>
       </c>
       <c r="M2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O2">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -16777,7 +17254,7 @@
         <v/>
       </c>
       <c r="J3" t="str">
-        <v>9.50</v>
+        <v>9.00</v>
       </c>
       <c r="K3" t="str">
         <v/>
@@ -16789,7 +17266,7 @@
         <v>0</v>
       </c>
       <c r="N3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O3">
         <v>0</v>
@@ -16824,7 +17301,7 @@
         <v/>
       </c>
       <c r="J4" t="str">
-        <v>10.00</v>
+        <v>9.50</v>
       </c>
       <c r="K4" t="str">
         <v/>
@@ -16839,7 +17316,7 @@
         <v>0</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -16871,7 +17348,7 @@
         <v/>
       </c>
       <c r="J5" t="str">
-        <v>10.00</v>
+        <v>9.50</v>
       </c>
       <c r="K5" t="str">
         <v/>
@@ -16880,7 +17357,7 @@
         <v/>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N5">
         <v>0</v>
@@ -16918,7 +17395,7 @@
         <v/>
       </c>
       <c r="J6" t="str">
-        <v>10.00</v>
+        <v>9.50</v>
       </c>
       <c r="K6" t="str">
         <v/>
@@ -16930,7 +17407,7 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -17012,7 +17489,7 @@
         <v/>
       </c>
       <c r="J8" t="str">
-        <v>10.00</v>
+        <v>9.50</v>
       </c>
       <c r="K8" t="str">
         <v/>
@@ -17021,7 +17498,7 @@
         <v/>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -17106,7 +17583,7 @@
         <v/>
       </c>
       <c r="J10" t="str">
-        <v>10.00</v>
+        <v>9.00</v>
       </c>
       <c r="K10" t="str">
         <v/>
@@ -17121,7 +17598,7 @@
         <v>0</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -17247,7 +17724,7 @@
         <v>13</v>
       </c>
       <c r="J13" t="str">
-        <v>9.00</v>
+        <v>8.00</v>
       </c>
       <c r="K13" t="str">
         <v>1</v>
@@ -17262,7 +17739,7 @@
         <v>1</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -17623,7 +18100,7 @@
         <v/>
       </c>
       <c r="J21" t="str">
-        <v>10.00</v>
+        <v>9.50</v>
       </c>
       <c r="K21" t="str">
         <v/>
@@ -17632,7 +18109,7 @@
         <v/>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N21">
         <v>0</v>
@@ -17670,7 +18147,7 @@
         <v/>
       </c>
       <c r="J22" t="str">
-        <v>10.00</v>
+        <v>9.50</v>
       </c>
       <c r="K22" t="str">
         <v/>
@@ -17685,7 +18162,7 @@
         <v>0</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -20772,7 +21249,7 @@
         <v/>
       </c>
       <c r="J88" t="str">
-        <v>10.00</v>
+        <v>9.00</v>
       </c>
       <c r="K88" t="str">
         <v/>
@@ -20784,10 +21261,10 @@
         <v>0</v>
       </c>
       <c r="N88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O88">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
@@ -21356,10 +21833,10 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>34387</v>
+        <v>22323</v>
       </c>
       <c r="B101" t="str">
-        <v>عمر عبدالرحمن بن يحيى سيدي بابا</v>
+        <v>عمر</v>
       </c>
       <c r="C101" t="str">
         <v>ثالث 2</v>
@@ -21403,61 +21880,202 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
+        <v>34387</v>
+      </c>
+      <c r="B102" t="str">
+        <v>عمر عبدالرحمن بن يحيى سيدي بابا</v>
+      </c>
+      <c r="C102" t="str">
+        <v>ثالث 2</v>
+      </c>
+      <c r="D102" t="str">
+        <v/>
+      </c>
+      <c r="E102" t="str">
+        <v/>
+      </c>
+      <c r="F102" t="str">
+        <v/>
+      </c>
+      <c r="G102" t="str">
+        <v/>
+      </c>
+      <c r="H102" t="str">
+        <v/>
+      </c>
+      <c r="I102" t="str">
+        <v/>
+      </c>
+      <c r="J102" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="K102" t="str">
+        <v/>
+      </c>
+      <c r="L102" t="str">
+        <v/>
+      </c>
+      <c r="M102">
+        <v>0</v>
+      </c>
+      <c r="N102">
+        <v>0</v>
+      </c>
+      <c r="O102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>11111</v>
+      </c>
+      <c r="B103" t="str">
+        <v>عمران</v>
+      </c>
+      <c r="C103" t="str">
+        <v>ثالث 1</v>
+      </c>
+      <c r="D103" t="str">
+        <v/>
+      </c>
+      <c r="E103" t="str">
+        <v/>
+      </c>
+      <c r="F103" t="str">
+        <v/>
+      </c>
+      <c r="G103" t="str">
+        <v/>
+      </c>
+      <c r="H103" t="str">
+        <v/>
+      </c>
+      <c r="I103" t="str">
+        <v/>
+      </c>
+      <c r="J103" t="str">
+        <v>9.50</v>
+      </c>
+      <c r="K103" t="str">
+        <v/>
+      </c>
+      <c r="L103" t="str">
+        <v/>
+      </c>
+      <c r="M103">
+        <v>0</v>
+      </c>
+      <c r="N103">
+        <v>1</v>
+      </c>
+      <c r="O103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>22222</v>
+      </c>
+      <c r="B104" t="str">
+        <v>لوى</v>
+      </c>
+      <c r="C104" t="str">
+        <v>ثالث 1</v>
+      </c>
+      <c r="D104" t="str">
+        <v/>
+      </c>
+      <c r="E104" t="str">
+        <v/>
+      </c>
+      <c r="F104" t="str">
+        <v/>
+      </c>
+      <c r="G104" t="str">
+        <v/>
+      </c>
+      <c r="H104" t="str">
+        <v/>
+      </c>
+      <c r="I104" t="str">
+        <v/>
+      </c>
+      <c r="J104" t="str">
+        <v>9.50</v>
+      </c>
+      <c r="K104" t="str">
+        <v/>
+      </c>
+      <c r="L104" t="str">
+        <v/>
+      </c>
+      <c r="M104">
+        <v>1</v>
+      </c>
+      <c r="N104">
+        <v>0</v>
+      </c>
+      <c r="O104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
         <v>55201</v>
       </c>
-      <c r="B102" t="str">
+      <c r="B105" t="str">
         <v>محمد حمزة محمود سليمان</v>
       </c>
-      <c r="C102" t="str">
+      <c r="C105" t="str">
         <v>ثالث 1</v>
       </c>
-      <c r="D102" t="str">
-        <v/>
-      </c>
-      <c r="E102" t="str">
-        <v/>
-      </c>
-      <c r="F102" t="str">
-        <v/>
-      </c>
-      <c r="G102" t="str">
-        <v/>
-      </c>
-      <c r="H102" t="str">
-        <v/>
-      </c>
-      <c r="I102" t="str">
-        <v/>
-      </c>
-      <c r="J102" t="str">
-        <v>10.00</v>
-      </c>
-      <c r="K102" t="str">
-        <v/>
-      </c>
-      <c r="L102" t="str">
-        <v/>
-      </c>
-      <c r="M102">
-        <v>0</v>
-      </c>
-      <c r="N102">
-        <v>0</v>
-      </c>
-      <c r="O102">
+      <c r="D105" t="str">
+        <v/>
+      </c>
+      <c r="E105" t="str">
+        <v/>
+      </c>
+      <c r="F105" t="str">
+        <v/>
+      </c>
+      <c r="G105" t="str">
+        <v/>
+      </c>
+      <c r="H105" t="str">
+        <v/>
+      </c>
+      <c r="I105" t="str">
+        <v/>
+      </c>
+      <c r="J105" t="str">
+        <v>9.50</v>
+      </c>
+      <c r="K105" t="str">
+        <v/>
+      </c>
+      <c r="L105" t="str">
+        <v/>
+      </c>
+      <c r="M105">
+        <v>1</v>
+      </c>
+      <c r="N105">
+        <v>0</v>
+      </c>
+      <c r="O105">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O102"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O105"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K102"/>
+  <dimension ref="A1:K105"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -21505,28 +22123,28 @@
         <v>ثالث 1</v>
       </c>
       <c r="D2" t="str">
-        <v>2.50</v>
+        <v>4.50</v>
       </c>
       <c r="E2" t="str">
-        <v>5.00</v>
+        <v>6.75</v>
       </c>
       <c r="F2" t="str">
-        <v>6.00</v>
+        <v>4.00</v>
       </c>
       <c r="G2" t="str">
-        <v>7.25</v>
+        <v>18.25</v>
       </c>
       <c r="H2" t="str">
-        <v>20.75</v>
+        <v>33.50</v>
       </c>
       <c r="I2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K2">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -21546,19 +22164,19 @@
         <v>5.00</v>
       </c>
       <c r="F3" t="str">
-        <v>9.50</v>
+        <v>9.00</v>
       </c>
       <c r="G3" t="str">
         <v>8.00</v>
       </c>
       <c r="H3" t="str">
-        <v>25.00</v>
+        <v>24.50</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K3">
         <v>0</v>
@@ -21581,13 +22199,13 @@
         <v>5.00</v>
       </c>
       <c r="F4" t="str">
-        <v>10.00</v>
+        <v>9.50</v>
       </c>
       <c r="G4" t="str">
         <v>8.25</v>
       </c>
       <c r="H4" t="str">
-        <v>25.75</v>
+        <v>25.25</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -21596,7 +22214,7 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -21616,16 +22234,16 @@
         <v>5.00</v>
       </c>
       <c r="F5" t="str">
-        <v>10.00</v>
+        <v>9.50</v>
       </c>
       <c r="G5" t="str">
-        <v>3.50</v>
+        <v>3.25</v>
       </c>
       <c r="H5" t="str">
-        <v>21.00</v>
+        <v>20.25</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -21651,19 +22269,19 @@
         <v>5.00</v>
       </c>
       <c r="F6" t="str">
-        <v>10.00</v>
+        <v>9.50</v>
       </c>
       <c r="G6" t="str">
         <v>4.75</v>
       </c>
       <c r="H6" t="str">
-        <v>22.25</v>
+        <v>21.75</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6">
         <v>0</v>
@@ -21721,16 +22339,16 @@
         <v>4.33</v>
       </c>
       <c r="F8" t="str">
-        <v>10.00</v>
+        <v>9.50</v>
       </c>
       <c r="G8" t="str">
         <v>7.00</v>
       </c>
       <c r="H8" t="str">
-        <v>23.58</v>
+        <v>23.08</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -21791,13 +22409,13 @@
         <v>5.00</v>
       </c>
       <c r="F10" t="str">
-        <v>10.00</v>
+        <v>9.00</v>
       </c>
       <c r="G10" t="str">
         <v>5.25</v>
       </c>
       <c r="H10" t="str">
-        <v>22.75</v>
+        <v>21.75</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -21806,7 +22424,7 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -21858,7 +22476,7 @@
         <v>2.50</v>
       </c>
       <c r="E12" t="str">
-        <v>5.00</v>
+        <v>4.58</v>
       </c>
       <c r="F12" t="str">
         <v>10.00</v>
@@ -21867,7 +22485,7 @@
         <v>8.25</v>
       </c>
       <c r="H12" t="str">
-        <v>25.75</v>
+        <v>25.33</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -21896,13 +22514,13 @@
         <v>6.17</v>
       </c>
       <c r="F13" t="str">
-        <v>9.00</v>
+        <v>8.00</v>
       </c>
       <c r="G13" t="str">
         <v>16.00</v>
       </c>
       <c r="H13" t="str">
-        <v>37.42</v>
+        <v>36.42</v>
       </c>
       <c r="I13">
         <v>1</v>
@@ -21911,7 +22529,7 @@
         <v>1</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -22176,16 +22794,16 @@
         <v>5.00</v>
       </c>
       <c r="F21" t="str">
-        <v>10.00</v>
+        <v>9.50</v>
       </c>
       <c r="G21" t="str">
         <v>7.75</v>
       </c>
       <c r="H21" t="str">
-        <v>25.25</v>
+        <v>24.75</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -22211,13 +22829,13 @@
         <v>5.00</v>
       </c>
       <c r="F22" t="str">
-        <v>10.00</v>
+        <v>9.50</v>
       </c>
       <c r="G22" t="str">
         <v>3.50</v>
       </c>
       <c r="H22" t="str">
-        <v>22.67</v>
+        <v>22.17</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -22226,7 +22844,7 @@
         <v>0</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -24521,22 +25139,22 @@
         <v>5.00</v>
       </c>
       <c r="F88" t="str">
-        <v>10.00</v>
+        <v>9.00</v>
       </c>
       <c r="G88" t="str">
         <v>8.25</v>
       </c>
       <c r="H88" t="str">
-        <v>25.75</v>
+        <v>24.75</v>
       </c>
       <c r="I88">
         <v>0</v>
       </c>
       <c r="J88">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K88">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="89">
@@ -24961,10 +25579,10 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>34387</v>
+        <v>22323</v>
       </c>
       <c r="B101" t="str">
-        <v>عمر عبدالرحمن بن يحيى سيدي بابا</v>
+        <v>عمر</v>
       </c>
       <c r="C101" t="str">
         <v>ثالث 2</v>
@@ -24996,42 +25614,147 @@
     </row>
     <row r="102">
       <c r="A102" t="str">
+        <v>34387</v>
+      </c>
+      <c r="B102" t="str">
+        <v>عمر عبدالرحمن بن يحيى سيدي بابا</v>
+      </c>
+      <c r="C102" t="str">
+        <v>ثالث 2</v>
+      </c>
+      <c r="D102" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="E102" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="F102" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="G102" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="H102" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="I102">
+        <v>0</v>
+      </c>
+      <c r="J102">
+        <v>0</v>
+      </c>
+      <c r="K102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>11111</v>
+      </c>
+      <c r="B103" t="str">
+        <v>عمران</v>
+      </c>
+      <c r="C103" t="str">
+        <v>ثالث 1</v>
+      </c>
+      <c r="D103" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="E103" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="F103" t="str">
+        <v>9.50</v>
+      </c>
+      <c r="G103" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="H103" t="str">
+        <v>9.50</v>
+      </c>
+      <c r="I103">
+        <v>0</v>
+      </c>
+      <c r="J103">
+        <v>1</v>
+      </c>
+      <c r="K103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>22222</v>
+      </c>
+      <c r="B104" t="str">
+        <v>لوى</v>
+      </c>
+      <c r="C104" t="str">
+        <v>ثالث 1</v>
+      </c>
+      <c r="D104" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="E104" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="F104" t="str">
+        <v>9.50</v>
+      </c>
+      <c r="G104" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="H104" t="str">
+        <v>9.50</v>
+      </c>
+      <c r="I104">
+        <v>1</v>
+      </c>
+      <c r="J104">
+        <v>0</v>
+      </c>
+      <c r="K104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
         <v>55201</v>
       </c>
-      <c r="B102" t="str">
+      <c r="B105" t="str">
         <v>محمد حمزة محمود سليمان</v>
       </c>
-      <c r="C102" t="str">
+      <c r="C105" t="str">
         <v>ثالث 1</v>
       </c>
-      <c r="D102" t="str">
+      <c r="D105" t="str">
         <v>2.50</v>
       </c>
-      <c r="E102" t="str">
+      <c r="E105" t="str">
         <v>5.00</v>
       </c>
-      <c r="F102" t="str">
-        <v>10.00</v>
-      </c>
-      <c r="G102" t="str">
+      <c r="F105" t="str">
+        <v>9.50</v>
+      </c>
+      <c r="G105" t="str">
         <v>4.00</v>
       </c>
-      <c r="H102" t="str">
-        <v>21.50</v>
-      </c>
-      <c r="I102">
-        <v>0</v>
-      </c>
-      <c r="J102">
-        <v>0</v>
-      </c>
-      <c r="K102">
+      <c r="H105" t="str">
+        <v>21.00</v>
+      </c>
+      <c r="I105">
+        <v>1</v>
+      </c>
+      <c r="J105">
+        <v>0</v>
+      </c>
+      <c r="K105">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K102"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K105"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -515,7 +515,7 @@
         <v>10</v>
       </c>
       <c r="P2" t="str">
-        <v>4.00</v>
+        <v>4.50</v>
       </c>
       <c r="Q2" t="str">
         <v>15</v>
@@ -524,7 +524,7 @@
         <v>20</v>
       </c>
       <c r="S2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T2">
         <v>2</v>
@@ -543,14 +543,14 @@
       <c r="C3" t="str">
         <v>ثالث 1</v>
       </c>
-      <c r="D3">
-        <v>10</v>
-      </c>
-      <c r="E3">
-        <v>10</v>
-      </c>
-      <c r="F3">
-        <v>10</v>
+      <c r="D3" t="str">
+        <v>8</v>
+      </c>
+      <c r="E3" t="str">
+        <v>8</v>
+      </c>
+      <c r="F3" t="str">
+        <v>8</v>
       </c>
       <c r="G3">
         <v>10</v>
@@ -561,14 +561,14 @@
       <c r="I3">
         <v>10</v>
       </c>
-      <c r="J3">
-        <v>20</v>
-      </c>
-      <c r="K3">
-        <v>20</v>
-      </c>
-      <c r="L3">
-        <v>20</v>
+      <c r="J3" t="str">
+        <v>18</v>
+      </c>
+      <c r="K3" t="str">
+        <v>18</v>
+      </c>
+      <c r="L3" t="str">
+        <v>18</v>
       </c>
       <c r="M3">
         <v>20</v>
@@ -582,11 +582,11 @@
       <c r="P3" t="str">
         <v>9.00</v>
       </c>
-      <c r="Q3">
-        <v>14</v>
-      </c>
-      <c r="R3">
-        <v>18</v>
+      <c r="Q3" t="str">
+        <v>19</v>
+      </c>
+      <c r="R3" t="str">
+        <v>4</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -645,7 +645,7 @@
         <v>20</v>
       </c>
       <c r="P4" t="str">
-        <v>9.50</v>
+        <v>10.00</v>
       </c>
       <c r="Q4">
         <v>14</v>
@@ -660,7 +660,7 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -710,7 +710,7 @@
         <v>20</v>
       </c>
       <c r="P5" t="str">
-        <v>9.50</v>
+        <v>10.00</v>
       </c>
       <c r="Q5">
         <v>13</v>
@@ -719,7 +719,7 @@
         <v>0</v>
       </c>
       <c r="S5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -775,7 +775,7 @@
         <v>20</v>
       </c>
       <c r="P6" t="str">
-        <v>9.50</v>
+        <v>10.00</v>
       </c>
       <c r="Q6">
         <v>3</v>
@@ -787,7 +787,7 @@
         <v>0</v>
       </c>
       <c r="T6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U6">
         <v>0</v>
@@ -905,7 +905,7 @@
         <v>20</v>
       </c>
       <c r="P8" t="str">
-        <v>9.50</v>
+        <v>10.00</v>
       </c>
       <c r="Q8">
         <v>16</v>
@@ -914,7 +914,7 @@
         <v>12</v>
       </c>
       <c r="S8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>20</v>
       </c>
       <c r="P10" t="str">
-        <v>9.00</v>
+        <v>10.00</v>
       </c>
       <c r="Q10">
         <v>19</v>
@@ -1050,7 +1050,7 @@
         <v>0</v>
       </c>
       <c r="U10">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1230,7 +1230,7 @@
         <v>9</v>
       </c>
       <c r="P13" t="str">
-        <v>8.00</v>
+        <v>9.00</v>
       </c>
       <c r="Q13">
         <v>9</v>
@@ -1245,7 +1245,7 @@
         <v>1</v>
       </c>
       <c r="U13">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1750,7 +1750,7 @@
         <v>20</v>
       </c>
       <c r="P21" t="str">
-        <v>9.50</v>
+        <v>10.00</v>
       </c>
       <c r="Q21">
         <v>13</v>
@@ -1759,7 +1759,7 @@
         <v>18</v>
       </c>
       <c r="S21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T21">
         <v>0</v>
@@ -1815,7 +1815,7 @@
         <v>20</v>
       </c>
       <c r="P22" t="str">
-        <v>9.50</v>
+        <v>10.00</v>
       </c>
       <c r="Q22">
         <v>7</v>
@@ -1830,7 +1830,7 @@
         <v>0</v>
       </c>
       <c r="U22">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -6105,7 +6105,7 @@
         <v>20</v>
       </c>
       <c r="P88" t="str">
-        <v>9.00</v>
+        <v>10.00</v>
       </c>
       <c r="Q88">
         <v>19</v>
@@ -6117,10 +6117,10 @@
         <v>0</v>
       </c>
       <c r="T88">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U88">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -7080,7 +7080,7 @@
         <v/>
       </c>
       <c r="P103" t="str">
-        <v>9.50</v>
+        <v>10.00</v>
       </c>
       <c r="Q103" t="str">
         <v/>
@@ -7092,7 +7092,7 @@
         <v>0</v>
       </c>
       <c r="T103">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U103">
         <v>0</v>
@@ -7145,7 +7145,7 @@
         <v/>
       </c>
       <c r="P104" t="str">
-        <v>9.50</v>
+        <v>10.00</v>
       </c>
       <c r="Q104" t="str">
         <v/>
@@ -7154,7 +7154,7 @@
         <v/>
       </c>
       <c r="S104">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T104">
         <v>0</v>
@@ -7210,7 +7210,7 @@
         <v>20</v>
       </c>
       <c r="P105" t="str">
-        <v>9.50</v>
+        <v>10.00</v>
       </c>
       <c r="Q105">
         <v>4</v>
@@ -7219,7 +7219,7 @@
         <v>12</v>
       </c>
       <c r="S105">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T105">
         <v>0</v>
@@ -7315,7 +7315,7 @@
         <v>13</v>
       </c>
       <c r="J2" t="str">
-        <v>4.00</v>
+        <v>4.50</v>
       </c>
       <c r="K2" t="str">
         <v>18</v>
@@ -7324,7 +7324,7 @@
         <v>20</v>
       </c>
       <c r="M2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N2">
         <v>2</v>
@@ -7344,31 +7344,31 @@
         <v>ثالث 1</v>
       </c>
       <c r="D3" t="str">
-        <v/>
+        <v>10</v>
       </c>
       <c r="E3" t="str">
-        <v/>
+        <v>9</v>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>8</v>
       </c>
       <c r="G3" t="str">
-        <v/>
+        <v>20</v>
       </c>
       <c r="H3" t="str">
-        <v/>
+        <v>19</v>
       </c>
       <c r="I3" t="str">
-        <v/>
+        <v>18</v>
       </c>
       <c r="J3" t="str">
         <v>9.00</v>
       </c>
       <c r="K3" t="str">
-        <v/>
+        <v>19</v>
       </c>
       <c r="L3" t="str">
-        <v/>
+        <v>3</v>
       </c>
       <c r="M3">
         <v>0</v>
@@ -7409,7 +7409,7 @@
         <v/>
       </c>
       <c r="J4" t="str">
-        <v>9.50</v>
+        <v>10.00</v>
       </c>
       <c r="K4" t="str">
         <v/>
@@ -7424,7 +7424,7 @@
         <v>0</v>
       </c>
       <c r="O4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -7456,7 +7456,7 @@
         <v/>
       </c>
       <c r="J5" t="str">
-        <v>9.50</v>
+        <v>10.00</v>
       </c>
       <c r="K5" t="str">
         <v/>
@@ -7465,7 +7465,7 @@
         <v/>
       </c>
       <c r="M5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5">
         <v>0</v>
@@ -7503,7 +7503,7 @@
         <v/>
       </c>
       <c r="J6" t="str">
-        <v>9.50</v>
+        <v>10.00</v>
       </c>
       <c r="K6" t="str">
         <v/>
@@ -7515,7 +7515,7 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -7597,7 +7597,7 @@
         <v/>
       </c>
       <c r="J8" t="str">
-        <v>9.50</v>
+        <v>10.00</v>
       </c>
       <c r="K8" t="str">
         <v/>
@@ -7606,7 +7606,7 @@
         <v/>
       </c>
       <c r="M8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -7691,7 +7691,7 @@
         <v/>
       </c>
       <c r="J10" t="str">
-        <v>9.00</v>
+        <v>10.00</v>
       </c>
       <c r="K10" t="str">
         <v/>
@@ -7706,7 +7706,7 @@
         <v>0</v>
       </c>
       <c r="O10">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -7832,7 +7832,7 @@
         <v>3</v>
       </c>
       <c r="J13" t="str">
-        <v>8.00</v>
+        <v>9.00</v>
       </c>
       <c r="K13" t="str">
         <v>9</v>
@@ -7847,7 +7847,7 @@
         <v>1</v>
       </c>
       <c r="O13">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -8208,7 +8208,7 @@
         <v/>
       </c>
       <c r="J21" t="str">
-        <v>9.50</v>
+        <v>10.00</v>
       </c>
       <c r="K21" t="str">
         <v/>
@@ -8217,7 +8217,7 @@
         <v/>
       </c>
       <c r="M21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21">
         <v>0</v>
@@ -8255,7 +8255,7 @@
         <v/>
       </c>
       <c r="J22" t="str">
-        <v>9.50</v>
+        <v>10.00</v>
       </c>
       <c r="K22" t="str">
         <v/>
@@ -8270,7 +8270,7 @@
         <v>0</v>
       </c>
       <c r="O22">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -11357,7 +11357,7 @@
         <v/>
       </c>
       <c r="J88" t="str">
-        <v>9.00</v>
+        <v>10.00</v>
       </c>
       <c r="K88" t="str">
         <v/>
@@ -11369,10 +11369,10 @@
         <v>0</v>
       </c>
       <c r="N88">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O88">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -12062,7 +12062,7 @@
         <v/>
       </c>
       <c r="J103" t="str">
-        <v>9.50</v>
+        <v>10.00</v>
       </c>
       <c r="K103" t="str">
         <v/>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="N103">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O103">
         <v>0</v>
@@ -12109,7 +12109,7 @@
         <v/>
       </c>
       <c r="J104" t="str">
-        <v>9.50</v>
+        <v>10.00</v>
       </c>
       <c r="K104" t="str">
         <v/>
@@ -12118,7 +12118,7 @@
         <v/>
       </c>
       <c r="M104">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N104">
         <v>0</v>
@@ -12156,7 +12156,7 @@
         <v/>
       </c>
       <c r="J105" t="str">
-        <v>9.50</v>
+        <v>10.00</v>
       </c>
       <c r="K105" t="str">
         <v/>
@@ -12165,7 +12165,7 @@
         <v/>
       </c>
       <c r="M105">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N105">
         <v>0</v>
@@ -12261,7 +12261,7 @@
         <v/>
       </c>
       <c r="J2" t="str">
-        <v>4.00</v>
+        <v>4.50</v>
       </c>
       <c r="K2" t="str">
         <v/>
@@ -12270,7 +12270,7 @@
         <v/>
       </c>
       <c r="M2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N2">
         <v>2</v>
@@ -12355,7 +12355,7 @@
         <v/>
       </c>
       <c r="J4" t="str">
-        <v>9.50</v>
+        <v>10.00</v>
       </c>
       <c r="K4" t="str">
         <v/>
@@ -12370,7 +12370,7 @@
         <v>0</v>
       </c>
       <c r="O4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -12402,7 +12402,7 @@
         <v/>
       </c>
       <c r="J5" t="str">
-        <v>9.50</v>
+        <v>10.00</v>
       </c>
       <c r="K5" t="str">
         <v/>
@@ -12411,7 +12411,7 @@
         <v/>
       </c>
       <c r="M5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5">
         <v>0</v>
@@ -12449,7 +12449,7 @@
         <v/>
       </c>
       <c r="J6" t="str">
-        <v>9.50</v>
+        <v>10.00</v>
       </c>
       <c r="K6" t="str">
         <v/>
@@ -12461,7 +12461,7 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -12543,7 +12543,7 @@
         <v/>
       </c>
       <c r="J8" t="str">
-        <v>9.50</v>
+        <v>10.00</v>
       </c>
       <c r="K8" t="str">
         <v/>
@@ -12552,7 +12552,7 @@
         <v/>
       </c>
       <c r="M8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -12637,7 +12637,7 @@
         <v/>
       </c>
       <c r="J10" t="str">
-        <v>9.00</v>
+        <v>10.00</v>
       </c>
       <c r="K10" t="str">
         <v/>
@@ -12652,7 +12652,7 @@
         <v>0</v>
       </c>
       <c r="O10">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -12778,7 +12778,7 @@
         <v>4</v>
       </c>
       <c r="J13" t="str">
-        <v>8.00</v>
+        <v>9.00</v>
       </c>
       <c r="K13" t="str">
         <v>20</v>
@@ -12793,7 +12793,7 @@
         <v>1</v>
       </c>
       <c r="O13">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -13154,7 +13154,7 @@
         <v/>
       </c>
       <c r="J21" t="str">
-        <v>9.50</v>
+        <v>10.00</v>
       </c>
       <c r="K21" t="str">
         <v/>
@@ -13163,7 +13163,7 @@
         <v/>
       </c>
       <c r="M21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21">
         <v>0</v>
@@ -13201,7 +13201,7 @@
         <v/>
       </c>
       <c r="J22" t="str">
-        <v>9.50</v>
+        <v>10.00</v>
       </c>
       <c r="K22" t="str">
         <v/>
@@ -13216,7 +13216,7 @@
         <v>0</v>
       </c>
       <c r="O22">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -16303,7 +16303,7 @@
         <v/>
       </c>
       <c r="J88" t="str">
-        <v>9.00</v>
+        <v>10.00</v>
       </c>
       <c r="K88" t="str">
         <v/>
@@ -16315,10 +16315,10 @@
         <v>0</v>
       </c>
       <c r="N88">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O88">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -17008,7 +17008,7 @@
         <v/>
       </c>
       <c r="J103" t="str">
-        <v>9.50</v>
+        <v>10.00</v>
       </c>
       <c r="K103" t="str">
         <v/>
@@ -17020,7 +17020,7 @@
         <v>0</v>
       </c>
       <c r="N103">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O103">
         <v>0</v>
@@ -17055,7 +17055,7 @@
         <v/>
       </c>
       <c r="J104" t="str">
-        <v>9.50</v>
+        <v>10.00</v>
       </c>
       <c r="K104" t="str">
         <v/>
@@ -17064,7 +17064,7 @@
         <v/>
       </c>
       <c r="M104">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N104">
         <v>0</v>
@@ -17102,7 +17102,7 @@
         <v/>
       </c>
       <c r="J105" t="str">
-        <v>9.50</v>
+        <v>10.00</v>
       </c>
       <c r="K105" t="str">
         <v/>
@@ -17111,7 +17111,7 @@
         <v/>
       </c>
       <c r="M105">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N105">
         <v>0</v>
@@ -17207,7 +17207,7 @@
         <v/>
       </c>
       <c r="J2" t="str">
-        <v>4.00</v>
+        <v>4.50</v>
       </c>
       <c r="K2" t="str">
         <v/>
@@ -17216,7 +17216,7 @@
         <v/>
       </c>
       <c r="M2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N2">
         <v>2</v>
@@ -17301,7 +17301,7 @@
         <v/>
       </c>
       <c r="J4" t="str">
-        <v>9.50</v>
+        <v>10.00</v>
       </c>
       <c r="K4" t="str">
         <v/>
@@ -17316,7 +17316,7 @@
         <v>0</v>
       </c>
       <c r="O4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -17348,7 +17348,7 @@
         <v/>
       </c>
       <c r="J5" t="str">
-        <v>9.50</v>
+        <v>10.00</v>
       </c>
       <c r="K5" t="str">
         <v/>
@@ -17357,7 +17357,7 @@
         <v/>
       </c>
       <c r="M5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N5">
         <v>0</v>
@@ -17395,7 +17395,7 @@
         <v/>
       </c>
       <c r="J6" t="str">
-        <v>9.50</v>
+        <v>10.00</v>
       </c>
       <c r="K6" t="str">
         <v/>
@@ -17407,7 +17407,7 @@
         <v>0</v>
       </c>
       <c r="N6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6">
         <v>0</v>
@@ -17489,7 +17489,7 @@
         <v/>
       </c>
       <c r="J8" t="str">
-        <v>9.50</v>
+        <v>10.00</v>
       </c>
       <c r="K8" t="str">
         <v/>
@@ -17498,7 +17498,7 @@
         <v/>
       </c>
       <c r="M8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -17583,7 +17583,7 @@
         <v/>
       </c>
       <c r="J10" t="str">
-        <v>9.00</v>
+        <v>10.00</v>
       </c>
       <c r="K10" t="str">
         <v/>
@@ -17598,7 +17598,7 @@
         <v>0</v>
       </c>
       <c r="O10">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -17724,7 +17724,7 @@
         <v>13</v>
       </c>
       <c r="J13" t="str">
-        <v>8.00</v>
+        <v>9.00</v>
       </c>
       <c r="K13" t="str">
         <v>1</v>
@@ -17739,7 +17739,7 @@
         <v>1</v>
       </c>
       <c r="O13">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -18100,7 +18100,7 @@
         <v/>
       </c>
       <c r="J21" t="str">
-        <v>9.50</v>
+        <v>10.00</v>
       </c>
       <c r="K21" t="str">
         <v/>
@@ -18109,7 +18109,7 @@
         <v/>
       </c>
       <c r="M21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21">
         <v>0</v>
@@ -18147,7 +18147,7 @@
         <v/>
       </c>
       <c r="J22" t="str">
-        <v>9.50</v>
+        <v>10.00</v>
       </c>
       <c r="K22" t="str">
         <v/>
@@ -18162,7 +18162,7 @@
         <v>0</v>
       </c>
       <c r="O22">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -21249,7 +21249,7 @@
         <v/>
       </c>
       <c r="J88" t="str">
-        <v>9.00</v>
+        <v>10.00</v>
       </c>
       <c r="K88" t="str">
         <v/>
@@ -21261,10 +21261,10 @@
         <v>0</v>
       </c>
       <c r="N88">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O88">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -21954,7 +21954,7 @@
         <v/>
       </c>
       <c r="J103" t="str">
-        <v>9.50</v>
+        <v>10.00</v>
       </c>
       <c r="K103" t="str">
         <v/>
@@ -21966,7 +21966,7 @@
         <v>0</v>
       </c>
       <c r="N103">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O103">
         <v>0</v>
@@ -22001,7 +22001,7 @@
         <v/>
       </c>
       <c r="J104" t="str">
-        <v>9.50</v>
+        <v>10.00</v>
       </c>
       <c r="K104" t="str">
         <v/>
@@ -22010,7 +22010,7 @@
         <v/>
       </c>
       <c r="M104">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N104">
         <v>0</v>
@@ -22048,7 +22048,7 @@
         <v/>
       </c>
       <c r="J105" t="str">
-        <v>9.50</v>
+        <v>10.00</v>
       </c>
       <c r="K105" t="str">
         <v/>
@@ -22057,7 +22057,7 @@
         <v/>
       </c>
       <c r="M105">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N105">
         <v>0</v>
@@ -22123,22 +22123,22 @@
         <v>ثالث 1</v>
       </c>
       <c r="D2" t="str">
-        <v>4.50</v>
+        <v>5.00</v>
       </c>
       <c r="E2" t="str">
-        <v>6.75</v>
+        <v>10.00</v>
       </c>
       <c r="F2" t="str">
-        <v>4.00</v>
+        <v>7.25</v>
       </c>
       <c r="G2" t="str">
-        <v>18.25</v>
+        <v>10.00</v>
       </c>
       <c r="H2" t="str">
-        <v>33.50</v>
+        <v>32.25</v>
       </c>
       <c r="I2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J2">
         <v>2</v>
@@ -22158,19 +22158,19 @@
         <v>ثالث 1</v>
       </c>
       <c r="D3" t="str">
-        <v>2.50</v>
+        <v>5.00</v>
       </c>
       <c r="E3" t="str">
-        <v>5.00</v>
+        <v>10.00</v>
       </c>
       <c r="F3" t="str">
-        <v>9.00</v>
+        <v>9.25</v>
       </c>
       <c r="G3" t="str">
-        <v>8.00</v>
+        <v>10.00</v>
       </c>
       <c r="H3" t="str">
-        <v>24.50</v>
+        <v>34.25</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -22199,13 +22199,13 @@
         <v>5.00</v>
       </c>
       <c r="F4" t="str">
-        <v>9.50</v>
+        <v>10.00</v>
       </c>
       <c r="G4" t="str">
-        <v>8.25</v>
+        <v>5.00</v>
       </c>
       <c r="H4" t="str">
-        <v>25.25</v>
+        <v>22.50</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -22214,7 +22214,7 @@
         <v>0</v>
       </c>
       <c r="K4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -22234,16 +22234,16 @@
         <v>5.00</v>
       </c>
       <c r="F5" t="str">
-        <v>9.50</v>
+        <v>10.00</v>
       </c>
       <c r="G5" t="str">
         <v>3.25</v>
       </c>
       <c r="H5" t="str">
-        <v>20.25</v>
+        <v>20.75</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -22269,19 +22269,19 @@
         <v>5.00</v>
       </c>
       <c r="F6" t="str">
-        <v>9.50</v>
+        <v>10.00</v>
       </c>
       <c r="G6" t="str">
         <v>4.75</v>
       </c>
       <c r="H6" t="str">
-        <v>21.75</v>
+        <v>22.25</v>
       </c>
       <c r="I6">
         <v>0</v>
       </c>
       <c r="J6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K6">
         <v>0</v>
@@ -22333,22 +22333,22 @@
         <v>ثالث 1</v>
       </c>
       <c r="D8" t="str">
-        <v>2.25</v>
+        <v>2.50</v>
       </c>
       <c r="E8" t="str">
-        <v>4.33</v>
+        <v>5.00</v>
       </c>
       <c r="F8" t="str">
-        <v>9.50</v>
+        <v>10.00</v>
       </c>
       <c r="G8" t="str">
-        <v>7.00</v>
+        <v>5.00</v>
       </c>
       <c r="H8" t="str">
-        <v>23.08</v>
+        <v>22.50</v>
       </c>
       <c r="I8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -22409,13 +22409,13 @@
         <v>5.00</v>
       </c>
       <c r="F10" t="str">
-        <v>9.00</v>
+        <v>10.00</v>
       </c>
       <c r="G10" t="str">
-        <v>5.25</v>
+        <v>5.00</v>
       </c>
       <c r="H10" t="str">
-        <v>21.75</v>
+        <v>22.50</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -22424,7 +22424,7 @@
         <v>0</v>
       </c>
       <c r="K10">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -22447,10 +22447,10 @@
         <v>10.00</v>
       </c>
       <c r="G11" t="str">
-        <v>6.50</v>
+        <v>5.00</v>
       </c>
       <c r="H11" t="str">
-        <v>24.00</v>
+        <v>22.50</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -22476,16 +22476,16 @@
         <v>2.50</v>
       </c>
       <c r="E12" t="str">
-        <v>4.58</v>
+        <v>5.00</v>
       </c>
       <c r="F12" t="str">
         <v>10.00</v>
       </c>
       <c r="G12" t="str">
-        <v>8.25</v>
+        <v>5.00</v>
       </c>
       <c r="H12" t="str">
-        <v>25.33</v>
+        <v>22.50</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -22511,16 +22511,16 @@
         <v>6.25</v>
       </c>
       <c r="E13" t="str">
-        <v>6.17</v>
+        <v>8.67</v>
       </c>
       <c r="F13" t="str">
-        <v>8.00</v>
+        <v>9.25</v>
       </c>
       <c r="G13" t="str">
-        <v>16.00</v>
+        <v>13.25</v>
       </c>
       <c r="H13" t="str">
-        <v>36.42</v>
+        <v>37.42</v>
       </c>
       <c r="I13">
         <v>1</v>
@@ -22529,7 +22529,7 @@
         <v>1</v>
       </c>
       <c r="K13">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -22619,13 +22619,13 @@
         <v>5.00</v>
       </c>
       <c r="F16" t="str">
-        <v>9.50</v>
+        <v>9.63</v>
       </c>
       <c r="G16" t="str">
-        <v>8.25</v>
+        <v>5.00</v>
       </c>
       <c r="H16" t="str">
-        <v>26.25</v>
+        <v>23.13</v>
       </c>
       <c r="I16">
         <v>1</v>
@@ -22724,10 +22724,10 @@
         <v>5.00</v>
       </c>
       <c r="F19" t="str">
-        <v>9.50</v>
+        <v>9.63</v>
       </c>
       <c r="G19" t="str">
-        <v>4.25</v>
+        <v>4.13</v>
       </c>
       <c r="H19" t="str">
         <v>22.50</v>
@@ -22759,13 +22759,13 @@
         <v>5.00</v>
       </c>
       <c r="F20" t="str">
-        <v>9.50</v>
+        <v>9.63</v>
       </c>
       <c r="G20" t="str">
-        <v>6.00</v>
+        <v>5.00</v>
       </c>
       <c r="H20" t="str">
-        <v>24.17</v>
+        <v>23.29</v>
       </c>
       <c r="I20">
         <v>1</v>
@@ -22794,16 +22794,16 @@
         <v>5.00</v>
       </c>
       <c r="F21" t="str">
-        <v>9.50</v>
+        <v>10.00</v>
       </c>
       <c r="G21" t="str">
-        <v>7.75</v>
+        <v>5.00</v>
       </c>
       <c r="H21" t="str">
-        <v>24.75</v>
+        <v>22.50</v>
       </c>
       <c r="I21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -22829,13 +22829,13 @@
         <v>5.00</v>
       </c>
       <c r="F22" t="str">
-        <v>9.50</v>
+        <v>10.00</v>
       </c>
       <c r="G22" t="str">
         <v>3.50</v>
       </c>
       <c r="H22" t="str">
-        <v>22.17</v>
+        <v>22.67</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -22844,7 +22844,7 @@
         <v>0</v>
       </c>
       <c r="K22">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -22937,10 +22937,10 @@
         <v>10.00</v>
       </c>
       <c r="G25" t="str">
-        <v>8.75</v>
+        <v>5.00</v>
       </c>
       <c r="H25" t="str">
-        <v>26.25</v>
+        <v>22.50</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -23004,10 +23004,10 @@
         <v>5.00</v>
       </c>
       <c r="F27" t="str">
-        <v>9.50</v>
+        <v>9.63</v>
       </c>
       <c r="G27" t="str">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="H27" t="str">
         <v>21.50</v>
@@ -23042,10 +23042,10 @@
         <v>10.00</v>
       </c>
       <c r="G28" t="str">
-        <v>7.25</v>
+        <v>5.00</v>
       </c>
       <c r="H28" t="str">
-        <v>24.75</v>
+        <v>22.50</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -23077,10 +23077,10 @@
         <v>10.00</v>
       </c>
       <c r="G29" t="str">
-        <v>5.25</v>
+        <v>5.00</v>
       </c>
       <c r="H29" t="str">
-        <v>22.75</v>
+        <v>22.50</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -23112,10 +23112,10 @@
         <v>10.00</v>
       </c>
       <c r="G30" t="str">
-        <v>5.75</v>
+        <v>5.00</v>
       </c>
       <c r="H30" t="str">
-        <v>23.25</v>
+        <v>22.50</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -23182,10 +23182,10 @@
         <v>10.00</v>
       </c>
       <c r="G32" t="str">
-        <v>5.50</v>
+        <v>5.00</v>
       </c>
       <c r="H32" t="str">
-        <v>23.00</v>
+        <v>22.50</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -23252,10 +23252,10 @@
         <v>10.00</v>
       </c>
       <c r="G34" t="str">
-        <v>6.00</v>
+        <v>5.00</v>
       </c>
       <c r="H34" t="str">
-        <v>23.50</v>
+        <v>22.50</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -23287,10 +23287,10 @@
         <v>10.00</v>
       </c>
       <c r="G35" t="str">
-        <v>5.25</v>
+        <v>5.00</v>
       </c>
       <c r="H35" t="str">
-        <v>22.75</v>
+        <v>22.50</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -25139,22 +25139,22 @@
         <v>5.00</v>
       </c>
       <c r="F88" t="str">
-        <v>9.00</v>
+        <v>10.00</v>
       </c>
       <c r="G88" t="str">
-        <v>8.25</v>
+        <v>5.00</v>
       </c>
       <c r="H88" t="str">
-        <v>24.75</v>
+        <v>22.50</v>
       </c>
       <c r="I88">
         <v>0</v>
       </c>
       <c r="J88">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K88">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -25664,19 +25664,19 @@
         <v>0.00</v>
       </c>
       <c r="F103" t="str">
-        <v>9.50</v>
+        <v>10.00</v>
       </c>
       <c r="G103" t="str">
         <v>0.00</v>
       </c>
       <c r="H103" t="str">
-        <v>9.50</v>
+        <v>10.00</v>
       </c>
       <c r="I103">
         <v>0</v>
       </c>
       <c r="J103">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K103">
         <v>0</v>
@@ -25699,16 +25699,16 @@
         <v>0.00</v>
       </c>
       <c r="F104" t="str">
-        <v>9.50</v>
+        <v>10.00</v>
       </c>
       <c r="G104" t="str">
         <v>0.00</v>
       </c>
       <c r="H104" t="str">
-        <v>9.50</v>
+        <v>10.00</v>
       </c>
       <c r="I104">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J104">
         <v>0</v>
@@ -25734,16 +25734,16 @@
         <v>5.00</v>
       </c>
       <c r="F105" t="str">
-        <v>9.50</v>
+        <v>10.00</v>
       </c>
       <c r="G105" t="str">
         <v>4.00</v>
       </c>
       <c r="H105" t="str">
-        <v>21.00</v>
+        <v>21.50</v>
       </c>
       <c r="I105">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J105">
         <v>0</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -549,61 +549,61 @@
         <v>ثالث 1</v>
       </c>
       <c r="D3" t="str">
-        <v/>
+        <v>10</v>
       </c>
       <c r="E3" t="str">
-        <v/>
+        <v>10</v>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>2</v>
       </c>
       <c r="G3" t="str">
-        <v>0.00</v>
+        <v>7.33</v>
       </c>
       <c r="H3" t="str">
-        <v/>
+        <v>20</v>
       </c>
       <c r="I3" t="str">
-        <v/>
+        <v>6</v>
       </c>
       <c r="J3" t="str">
-        <v/>
+        <v>19</v>
       </c>
       <c r="K3" t="str">
-        <v>0.00</v>
+        <v>15.00</v>
       </c>
       <c r="L3">
         <v>0</v>
       </c>
       <c r="M3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N3">
         <v>0</v>
       </c>
       <c r="O3" t="str">
-        <v>10.00</v>
+        <v>9.50</v>
       </c>
       <c r="P3" t="str">
-        <v/>
+        <v>0</v>
       </c>
       <c r="Q3" t="str">
-        <v/>
+        <v>20</v>
       </c>
       <c r="R3" t="str">
-        <v>0.00</v>
+        <v>7.33</v>
       </c>
       <c r="S3" t="str">
-        <v>0.00</v>
+        <v>15.00</v>
       </c>
       <c r="T3" t="str">
         <v>10.00</v>
       </c>
       <c r="U3" t="str">
-        <v>0.00</v>
+        <v>19.50</v>
       </c>
       <c r="V3" t="str">
-        <v>10.00</v>
+        <v>51.83</v>
       </c>
     </row>
     <row r="4">
@@ -868,7 +868,7 @@
         <v>16.50</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O2">
         <v>0</v>
@@ -877,7 +877,7 @@
         <v>0</v>
       </c>
       <c r="Q2" t="str">
-        <v>10.00</v>
+        <v>9.00</v>
       </c>
       <c r="R2" t="str">
         <v>10</v>
@@ -892,13 +892,13 @@
         <v>16.50</v>
       </c>
       <c r="V2" t="str">
-        <v>10.00</v>
+        <v>9.00</v>
       </c>
       <c r="W2" t="str">
         <v>10.00</v>
       </c>
       <c r="X2" t="str">
-        <v>41.00</v>
+        <v>40.00</v>
       </c>
     </row>
     <row r="3">
@@ -912,34 +912,34 @@
         <v>ثالث 1</v>
       </c>
       <c r="D3" t="str">
-        <v/>
+        <v>4</v>
       </c>
       <c r="E3" t="str">
-        <v/>
+        <v>9</v>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>7</v>
       </c>
       <c r="G3" t="str">
-        <v/>
+        <v>7</v>
       </c>
       <c r="H3" t="str">
-        <v>0.00</v>
+        <v>6.75</v>
       </c>
       <c r="I3" t="str">
-        <v/>
+        <v>10</v>
       </c>
       <c r="J3" t="str">
-        <v/>
+        <v>2</v>
       </c>
       <c r="K3" t="str">
-        <v/>
+        <v>9</v>
       </c>
       <c r="L3" t="str">
-        <v/>
+        <v>20</v>
       </c>
       <c r="M3" t="str">
-        <v>0.00</v>
+        <v>10.25</v>
       </c>
       <c r="N3">
         <v>0</v>
@@ -954,25 +954,25 @@
         <v>10.00</v>
       </c>
       <c r="R3" t="str">
-        <v/>
+        <v>19</v>
       </c>
       <c r="S3" t="str">
-        <v/>
+        <v>20</v>
       </c>
       <c r="T3" t="str">
-        <v>0.00</v>
+        <v>10.00</v>
       </c>
       <c r="U3" t="str">
-        <v>0.00</v>
+        <v>20.00</v>
       </c>
       <c r="V3" t="str">
         <v>10.00</v>
       </c>
       <c r="W3" t="str">
-        <v>0.00</v>
+        <v>20.00</v>
       </c>
       <c r="X3" t="str">
-        <v>10.00</v>
+        <v>60.00</v>
       </c>
     </row>
     <row r="4">
@@ -1305,40 +1305,40 @@
         <v>ثالث 1</v>
       </c>
       <c r="D3" t="str">
-        <v/>
+        <v>4</v>
       </c>
       <c r="E3" t="str">
-        <v/>
+        <v>2</v>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>8</v>
       </c>
       <c r="G3" t="str">
-        <v/>
+        <v>1</v>
       </c>
       <c r="H3" t="str">
-        <v/>
+        <v>10</v>
       </c>
       <c r="I3" t="str">
-        <v>0.00</v>
+        <v>5.00</v>
       </c>
       <c r="J3" t="str">
-        <v/>
+        <v>20</v>
       </c>
       <c r="K3" t="str">
-        <v/>
+        <v>20</v>
       </c>
       <c r="L3" t="str">
-        <v/>
+        <v>20</v>
       </c>
       <c r="M3" t="str">
-        <v/>
+        <v>10</v>
       </c>
       <c r="N3" t="str">
-        <v/>
+        <v>10</v>
       </c>
       <c r="O3" t="str">
-        <v>0.00</v>
+        <v>16.00</v>
       </c>
       <c r="P3">
         <v>0</v>
@@ -1353,25 +1353,25 @@
         <v>10.00</v>
       </c>
       <c r="T3" t="str">
-        <v/>
+        <v>11</v>
       </c>
       <c r="U3" t="str">
         <v/>
       </c>
       <c r="V3" t="str">
-        <v>0.00</v>
+        <v>5.00</v>
       </c>
       <c r="W3" t="str">
-        <v>0.00</v>
+        <v>16.00</v>
       </c>
       <c r="X3" t="str">
         <v>10.00</v>
       </c>
       <c r="Y3" t="str">
-        <v>0.00</v>
+        <v>11.00</v>
       </c>
       <c r="Z3" t="str">
-        <v>10.00</v>
+        <v>42.00</v>
       </c>
     </row>
     <row r="4">
@@ -1588,13 +1588,13 @@
         <v>17.30</v>
       </c>
       <c r="F2" t="str">
-        <v>10.00</v>
+        <v>9.67</v>
       </c>
       <c r="G2" t="str">
         <v>16.50</v>
       </c>
       <c r="H2" t="str">
-        <v>51.63</v>
+        <v>51.30</v>
       </c>
     </row>
     <row r="3">
@@ -1608,19 +1608,19 @@
         <v>ثالث 1</v>
       </c>
       <c r="D3" t="str">
-        <v>0.00</v>
+        <v>7.44</v>
       </c>
       <c r="E3" t="str">
-        <v>0.00</v>
+        <v>17.00</v>
       </c>
       <c r="F3" t="str">
         <v>10.00</v>
       </c>
       <c r="G3" t="str">
-        <v>0.00</v>
+        <v>16.83</v>
       </c>
       <c r="H3" t="str">
-        <v>10.00</v>
+        <v>51.28</v>
       </c>
     </row>
     <row r="4">

--- a/data.xlsx
+++ b/data.xlsx
@@ -505,16 +505,16 @@
         <v>3.33</v>
       </c>
       <c r="L2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N2">
         <v>0</v>
       </c>
       <c r="O2" t="str">
-        <v>10.00</v>
+        <v>8.50</v>
       </c>
       <c r="P2" t="str">
         <v>11</v>
@@ -523,7 +523,7 @@
         <v>12</v>
       </c>
       <c r="R2" t="str">
-        <v>7.33</v>
+        <v>5.83</v>
       </c>
       <c r="S2" t="str">
         <v>3.33</v>
@@ -535,7 +535,7 @@
         <v>20.00</v>
       </c>
       <c r="V2" t="str">
-        <v>40.67</v>
+        <v>39.17</v>
       </c>
     </row>
     <row r="3">
@@ -1457,16 +1457,16 @@
         <v>6.33</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O16" t="str">
-        <v>10.00</v>
+        <v>7.00</v>
       </c>
       <c r="P16" t="str">
         <v>20</v>
@@ -7919,16 +7919,16 @@
         <v>7.80</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16">
         <v>0</v>
       </c>
       <c r="S16" t="str">
-        <v>10.00</v>
+        <v>8.50</v>
       </c>
       <c r="T16" t="str">
         <v>4</v>
@@ -7943,13 +7943,13 @@
         <v>7.80</v>
       </c>
       <c r="X16" t="str">
-        <v>10.00</v>
+        <v>8.50</v>
       </c>
       <c r="Y16" t="str">
         <v>16.00</v>
       </c>
       <c r="Z16" t="str">
-        <v>38.80</v>
+        <v>37.30</v>
       </c>
     </row>
     <row r="17">
@@ -10240,7 +10240,7 @@
         <v>ثالث 1</v>
       </c>
       <c r="D2" t="str">
-        <v>2.44</v>
+        <v>1.94</v>
       </c>
       <c r="E2" t="str">
         <v>1.11</v>
@@ -10252,7 +10252,7 @@
         <v>6.67</v>
       </c>
       <c r="H2" t="str">
-        <v>20.22</v>
+        <v>19.72</v>
       </c>
     </row>
     <row r="3">
@@ -10610,13 +10610,13 @@
         <v>10.60</v>
       </c>
       <c r="F16" t="str">
-        <v>10.00</v>
+        <v>9.50</v>
       </c>
       <c r="G16" t="str">
         <v>14.67</v>
       </c>
       <c r="H16" t="str">
-        <v>40.93</v>
+        <v>40.43</v>
       </c>
     </row>
     <row r="17">

--- a/data.xlsx
+++ b/data.xlsx
@@ -6,7 +6,8 @@
     <sheet name="الوحدة 1" sheetId="1" r:id="rId1"/>
     <sheet name="الوحدة 2" sheetId="2" r:id="rId2"/>
     <sheet name="الوحدة 3" sheetId="3" r:id="rId3"/>
-    <sheet name="خلاصة" sheetId="4" r:id="rId4"/>
+    <sheet name="الفصل 4" sheetId="4" r:id="rId4"/>
+    <sheet name="خلاصة" sheetId="5" r:id="rId5"/>
   </sheets>
 </workbook>
 </file>
@@ -10201,6 +10202,3009 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:V44"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>رقم</v>
+      </c>
+      <c r="B1" t="str">
+        <v>الاسم</v>
+      </c>
+      <c r="C1" t="str">
+        <v>الفصل</v>
+      </c>
+      <c r="D1" t="str">
+        <v>واجب درس 1</v>
+      </c>
+      <c r="E1" t="str">
+        <v>واجب درس 2</v>
+      </c>
+      <c r="F1" t="str">
+        <v>واجب درس 3</v>
+      </c>
+      <c r="G1" t="str">
+        <v>الموزونه</v>
+      </c>
+      <c r="H1" t="str">
+        <v>نشاط درس 1</v>
+      </c>
+      <c r="I1" t="str">
+        <v>نشاط درس 2</v>
+      </c>
+      <c r="J1" t="str">
+        <v>نشاط درس 3</v>
+      </c>
+      <c r="K1" t="str">
+        <v>الموزونه</v>
+      </c>
+      <c r="L1" t="str">
+        <v>غياب</v>
+      </c>
+      <c r="M1" t="str">
+        <v>تأخر</v>
+      </c>
+      <c r="N1" t="str">
+        <v>مخالفات</v>
+      </c>
+      <c r="O1" t="str">
+        <v>المشاركه</v>
+      </c>
+      <c r="P1" t="str">
+        <v>اختبار</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>مشروع</v>
+      </c>
+      <c r="R1" t="str">
+        <v>خ واجب</v>
+      </c>
+      <c r="S1" t="str">
+        <v>خ نشاط</v>
+      </c>
+      <c r="T1" t="str">
+        <v>خ مشاركه</v>
+      </c>
+      <c r="U1" t="str">
+        <v>خ اختبار</v>
+      </c>
+      <c r="V1" t="str">
+        <v>المجموع</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>00000</v>
+      </c>
+      <c r="B2" t="str">
+        <v>ااا</v>
+      </c>
+      <c r="C2" t="str">
+        <v>ثالث 1</v>
+      </c>
+      <c r="D2" t="str">
+        <v/>
+      </c>
+      <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="H2" t="str">
+        <v/>
+      </c>
+      <c r="I2" t="str">
+        <v/>
+      </c>
+      <c r="J2" t="str">
+        <v/>
+      </c>
+      <c r="K2" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="P2" t="str">
+        <v/>
+      </c>
+      <c r="Q2" t="str">
+        <v/>
+      </c>
+      <c r="R2" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="S2" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="T2" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="U2" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="V2" t="str">
+        <v>10.00</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>85734</v>
+      </c>
+      <c r="B3" t="str">
+        <v>ابراهيم بدر بن شتيان الجهني</v>
+      </c>
+      <c r="C3" t="str">
+        <v>ثالث 1</v>
+      </c>
+      <c r="D3" t="str">
+        <v/>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v/>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="L3">
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+      <c r="O3" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="P3" t="str">
+        <v/>
+      </c>
+      <c r="Q3" t="str">
+        <v/>
+      </c>
+      <c r="R3" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="S3" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="T3" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="U3" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="V3" t="str">
+        <v>10.00</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>09369</v>
+      </c>
+      <c r="B4" t="str">
+        <v>ابراهيم عبدالباقي بن الطاهر المناعي</v>
+      </c>
+      <c r="C4" t="str">
+        <v>ثالث 1</v>
+      </c>
+      <c r="D4" t="str">
+        <v/>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v/>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="P4" t="str">
+        <v/>
+      </c>
+      <c r="Q4" t="str">
+        <v/>
+      </c>
+      <c r="R4" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="S4" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="T4" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="U4" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="V4" t="str">
+        <v>10.00</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>87529</v>
+      </c>
+      <c r="B5" t="str">
+        <v>ابراهيم عبدالفتاح الحبيب</v>
+      </c>
+      <c r="C5" t="str">
+        <v>ثالث 1</v>
+      </c>
+      <c r="D5" t="str">
+        <v/>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v/>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="P5" t="str">
+        <v/>
+      </c>
+      <c r="Q5" t="str">
+        <v/>
+      </c>
+      <c r="R5" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="S5" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="T5" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="U5" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="V5" t="str">
+        <v>10.00</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>90719</v>
+      </c>
+      <c r="B6" t="str">
+        <v>ابراهيم فيصل عواد الجهني</v>
+      </c>
+      <c r="C6" t="str">
+        <v>ثالث 1</v>
+      </c>
+      <c r="D6" t="str">
+        <v/>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v/>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="L6">
+        <v>0</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+      <c r="O6" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="P6" t="str">
+        <v/>
+      </c>
+      <c r="Q6" t="str">
+        <v/>
+      </c>
+      <c r="R6" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="S6" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="T6" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="U6" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="V6" t="str">
+        <v>10.00</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>11780</v>
+      </c>
+      <c r="B7" t="str">
+        <v>ابراهيم محي الدين ابراهيم محمد الخير</v>
+      </c>
+      <c r="C7" t="str">
+        <v>ثالث 1</v>
+      </c>
+      <c r="D7" t="str">
+        <v/>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v/>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7">
+        <v>0</v>
+      </c>
+      <c r="O7" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="P7" t="str">
+        <v/>
+      </c>
+      <c r="Q7" t="str">
+        <v/>
+      </c>
+      <c r="R7" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="S7" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="T7" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="U7" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="V7" t="str">
+        <v>10.00</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>99092</v>
+      </c>
+      <c r="B8" t="str">
+        <v>احمد اسعد احمد الخضر</v>
+      </c>
+      <c r="C8" t="str">
+        <v>ثالث 1</v>
+      </c>
+      <c r="D8" t="str">
+        <v/>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v/>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="P8" t="str">
+        <v/>
+      </c>
+      <c r="Q8" t="str">
+        <v/>
+      </c>
+      <c r="R8" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="S8" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="T8" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="U8" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="V8" t="str">
+        <v>10.00</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>85505</v>
+      </c>
+      <c r="B9" t="str">
+        <v>احمد بركات حسين بركات</v>
+      </c>
+      <c r="C9" t="str">
+        <v>ثالث 1</v>
+      </c>
+      <c r="D9" t="str">
+        <v/>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v/>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="P9" t="str">
+        <v/>
+      </c>
+      <c r="Q9" t="str">
+        <v/>
+      </c>
+      <c r="R9" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="S9" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="T9" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="U9" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="V9" t="str">
+        <v>10.00</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>31549</v>
+      </c>
+      <c r="B10" t="str">
+        <v>احمد حامد بن محمد الينبعاوي</v>
+      </c>
+      <c r="C10" t="str">
+        <v>ثالث 1</v>
+      </c>
+      <c r="D10" t="str">
+        <v/>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v/>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="L10">
+        <v>0</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+      <c r="O10" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="P10" t="str">
+        <v/>
+      </c>
+      <c r="Q10" t="str">
+        <v/>
+      </c>
+      <c r="R10" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="S10" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="T10" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="U10" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="V10" t="str">
+        <v>10.00</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>12345</v>
+      </c>
+      <c r="B11" t="str">
+        <v>احمد خالد - عيساوي</v>
+      </c>
+      <c r="C11" t="str">
+        <v>ثالث 1</v>
+      </c>
+      <c r="D11" t="str">
+        <v/>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v/>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="P11" t="str">
+        <v/>
+      </c>
+      <c r="Q11" t="str">
+        <v/>
+      </c>
+      <c r="R11" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="S11" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="T11" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="U11" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="V11" t="str">
+        <v>10.00</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>36455</v>
+      </c>
+      <c r="B12" t="str">
+        <v>احمد عبد الله التوم عبد الله</v>
+      </c>
+      <c r="C12" t="str">
+        <v>ثالث 1</v>
+      </c>
+      <c r="D12" t="str">
+        <v/>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v/>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="P12" t="str">
+        <v/>
+      </c>
+      <c r="Q12" t="str">
+        <v/>
+      </c>
+      <c r="R12" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="S12" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="T12" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="U12" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="V12" t="str">
+        <v>10.00</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>44931</v>
+      </c>
+      <c r="B13" t="str">
+        <v>احمد عبدالوهاب العبيد العبدالله</v>
+      </c>
+      <c r="C13" t="str">
+        <v>ثالث 1</v>
+      </c>
+      <c r="D13" t="str">
+        <v/>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v/>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="P13" t="str">
+        <v/>
+      </c>
+      <c r="Q13" t="str">
+        <v/>
+      </c>
+      <c r="R13" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="S13" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="T13" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="U13" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="V13" t="str">
+        <v>10.00</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>85665</v>
+      </c>
+      <c r="B14" t="str">
+        <v>احمد نبيل عبدالرحمن سالم</v>
+      </c>
+      <c r="C14" t="str">
+        <v>ثالث 1</v>
+      </c>
+      <c r="D14" t="str">
+        <v/>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v/>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="L14">
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <v>0</v>
+      </c>
+      <c r="O14" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="P14" t="str">
+        <v/>
+      </c>
+      <c r="Q14" t="str">
+        <v/>
+      </c>
+      <c r="R14" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="S14" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="T14" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="U14" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="V14" t="str">
+        <v>10.00</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>46148</v>
+      </c>
+      <c r="B15" t="str">
+        <v>ادم سلطان عبدالودود الشعبي</v>
+      </c>
+      <c r="C15" t="str">
+        <v>ثالث 1</v>
+      </c>
+      <c r="D15" t="str">
+        <v/>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v/>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="L15">
+        <v>0</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="P15" t="str">
+        <v/>
+      </c>
+      <c r="Q15" t="str">
+        <v/>
+      </c>
+      <c r="R15" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="S15" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="T15" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="U15" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="V15" t="str">
+        <v>10.00</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>65020</v>
+      </c>
+      <c r="B16" t="str">
+        <v>اديب احمد مساعد الحجيلي</v>
+      </c>
+      <c r="C16" t="str">
+        <v>ثالث 1</v>
+      </c>
+      <c r="D16" t="str">
+        <v>1</v>
+      </c>
+      <c r="E16" t="str">
+        <v>2</v>
+      </c>
+      <c r="F16" t="str">
+        <v>3</v>
+      </c>
+      <c r="G16" t="str">
+        <v>2.00</v>
+      </c>
+      <c r="H16" t="str">
+        <v>9</v>
+      </c>
+      <c r="I16" t="str">
+        <v>8</v>
+      </c>
+      <c r="J16" t="str">
+        <v>7</v>
+      </c>
+      <c r="K16" t="str">
+        <v>8.00</v>
+      </c>
+      <c r="L16">
+        <v>0</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16">
+        <v>0</v>
+      </c>
+      <c r="O16" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="P16" t="str">
+        <v>10</v>
+      </c>
+      <c r="Q16" t="str">
+        <v>5</v>
+      </c>
+      <c r="R16" t="str">
+        <v>2.00</v>
+      </c>
+      <c r="S16" t="str">
+        <v>8.00</v>
+      </c>
+      <c r="T16" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="U16" t="str">
+        <v>15.00</v>
+      </c>
+      <c r="V16" t="str">
+        <v>35.00</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>39003</v>
+      </c>
+      <c r="B17" t="str">
+        <v>اسامه رضوان علوي ناجي</v>
+      </c>
+      <c r="C17" t="str">
+        <v>ثالث 1</v>
+      </c>
+      <c r="D17" t="str">
+        <v/>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v/>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="L17">
+        <v>0</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17">
+        <v>0</v>
+      </c>
+      <c r="O17" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="P17" t="str">
+        <v/>
+      </c>
+      <c r="Q17" t="str">
+        <v/>
+      </c>
+      <c r="R17" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="S17" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="T17" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="U17" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="V17" t="str">
+        <v>10.00</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>47319</v>
+      </c>
+      <c r="B18" t="str">
+        <v>اسامه عبدالرحمن بن خالد المسكتي</v>
+      </c>
+      <c r="C18" t="str">
+        <v>ثالث 1</v>
+      </c>
+      <c r="D18" t="str">
+        <v/>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v/>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="L18">
+        <v>0</v>
+      </c>
+      <c r="M18">
+        <v>0</v>
+      </c>
+      <c r="N18">
+        <v>0</v>
+      </c>
+      <c r="O18" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="P18" t="str">
+        <v/>
+      </c>
+      <c r="Q18" t="str">
+        <v/>
+      </c>
+      <c r="R18" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="S18" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="T18" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="U18" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="V18" t="str">
+        <v>10.00</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>77118</v>
+      </c>
+      <c r="B19" t="str">
+        <v>اسامه عبدالمجيد هاشم الحاج حميد</v>
+      </c>
+      <c r="C19" t="str">
+        <v>ثالث 1</v>
+      </c>
+      <c r="D19" t="str">
+        <v/>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <v/>
+      </c>
+      <c r="G19" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <v/>
+      </c>
+      <c r="J19" t="str">
+        <v/>
+      </c>
+      <c r="K19" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="L19">
+        <v>0</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>0</v>
+      </c>
+      <c r="O19" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="P19" t="str">
+        <v/>
+      </c>
+      <c r="Q19" t="str">
+        <v/>
+      </c>
+      <c r="R19" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="S19" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="T19" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="U19" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="V19" t="str">
+        <v>10.00</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>69497</v>
+      </c>
+      <c r="B20" t="str">
+        <v>أصيل احمد محمد الحلو</v>
+      </c>
+      <c r="C20" t="str">
+        <v>ثالث 1</v>
+      </c>
+      <c r="D20" t="str">
+        <v/>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v/>
+      </c>
+      <c r="J20" t="str">
+        <v/>
+      </c>
+      <c r="K20" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="P20" t="str">
+        <v/>
+      </c>
+      <c r="Q20" t="str">
+        <v/>
+      </c>
+      <c r="R20" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="S20" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="T20" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="U20" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="V20" t="str">
+        <v>10.00</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>15994</v>
+      </c>
+      <c r="B21" t="str">
+        <v>الحسن سالم علي دقاق</v>
+      </c>
+      <c r="C21" t="str">
+        <v>ثالث 1</v>
+      </c>
+      <c r="D21" t="str">
+        <v/>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
+        <v/>
+      </c>
+      <c r="G21" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
+        <v/>
+      </c>
+      <c r="J21" t="str">
+        <v/>
+      </c>
+      <c r="K21" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="P21" t="str">
+        <v/>
+      </c>
+      <c r="Q21" t="str">
+        <v/>
+      </c>
+      <c r="R21" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="S21" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="T21" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="U21" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="V21" t="str">
+        <v>10.00</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>15846</v>
+      </c>
+      <c r="B22" t="str">
+        <v>الوليد باسم محمد محمد</v>
+      </c>
+      <c r="C22" t="str">
+        <v>ثالث 1</v>
+      </c>
+      <c r="D22" t="str">
+        <v/>
+      </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
+      <c r="F22" t="str">
+        <v/>
+      </c>
+      <c r="G22" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
+      <c r="I22" t="str">
+        <v/>
+      </c>
+      <c r="J22" t="str">
+        <v/>
+      </c>
+      <c r="K22" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="L22">
+        <v>0</v>
+      </c>
+      <c r="M22">
+        <v>0</v>
+      </c>
+      <c r="N22">
+        <v>0</v>
+      </c>
+      <c r="O22" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="P22" t="str">
+        <v/>
+      </c>
+      <c r="Q22" t="str">
+        <v/>
+      </c>
+      <c r="R22" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="S22" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="T22" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="U22" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="V22" t="str">
+        <v>10.00</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>48852</v>
+      </c>
+      <c r="B23" t="str">
+        <v>الياس محمد عادل الحسن</v>
+      </c>
+      <c r="C23" t="str">
+        <v>ثالث 1</v>
+      </c>
+      <c r="D23" t="str">
+        <v/>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+      <c r="F23" t="str">
+        <v/>
+      </c>
+      <c r="G23" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <v/>
+      </c>
+      <c r="J23" t="str">
+        <v/>
+      </c>
+      <c r="K23" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="L23">
+        <v>0</v>
+      </c>
+      <c r="M23">
+        <v>0</v>
+      </c>
+      <c r="N23">
+        <v>0</v>
+      </c>
+      <c r="O23" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="P23" t="str">
+        <v/>
+      </c>
+      <c r="Q23" t="str">
+        <v/>
+      </c>
+      <c r="R23" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="S23" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="T23" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="U23" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="V23" t="str">
+        <v>10.00</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>32046</v>
+      </c>
+      <c r="B24" t="str">
+        <v>امير خلدون حسين كسرواني</v>
+      </c>
+      <c r="C24" t="str">
+        <v>ثالث 1</v>
+      </c>
+      <c r="D24" t="str">
+        <v/>
+      </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
+      <c r="F24" t="str">
+        <v/>
+      </c>
+      <c r="G24" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <v/>
+      </c>
+      <c r="J24" t="str">
+        <v/>
+      </c>
+      <c r="K24" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <v>0</v>
+      </c>
+      <c r="O24" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="P24" t="str">
+        <v/>
+      </c>
+      <c r="Q24" t="str">
+        <v/>
+      </c>
+      <c r="R24" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="S24" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="T24" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="U24" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="V24" t="str">
+        <v>10.00</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>95015</v>
+      </c>
+      <c r="B25" t="str">
+        <v>أنس أحمد - فقير بخش</v>
+      </c>
+      <c r="C25" t="str">
+        <v>ثالث 1</v>
+      </c>
+      <c r="D25" t="str">
+        <v/>
+      </c>
+      <c r="E25" t="str">
+        <v/>
+      </c>
+      <c r="F25" t="str">
+        <v/>
+      </c>
+      <c r="G25" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="H25" t="str">
+        <v/>
+      </c>
+      <c r="I25" t="str">
+        <v/>
+      </c>
+      <c r="J25" t="str">
+        <v/>
+      </c>
+      <c r="K25" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <v>0</v>
+      </c>
+      <c r="O25" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="P25" t="str">
+        <v/>
+      </c>
+      <c r="Q25" t="str">
+        <v/>
+      </c>
+      <c r="R25" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="S25" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="T25" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="U25" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="V25" t="str">
+        <v>10.00</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>83473</v>
+      </c>
+      <c r="B26" t="str">
+        <v>انس زكريا محمد الناجي</v>
+      </c>
+      <c r="C26" t="str">
+        <v>ثالث 1</v>
+      </c>
+      <c r="D26" t="str">
+        <v/>
+      </c>
+      <c r="E26" t="str">
+        <v/>
+      </c>
+      <c r="F26" t="str">
+        <v/>
+      </c>
+      <c r="G26" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="H26" t="str">
+        <v/>
+      </c>
+      <c r="I26" t="str">
+        <v/>
+      </c>
+      <c r="J26" t="str">
+        <v/>
+      </c>
+      <c r="K26" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <v>0</v>
+      </c>
+      <c r="O26" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="P26" t="str">
+        <v/>
+      </c>
+      <c r="Q26" t="str">
+        <v/>
+      </c>
+      <c r="R26" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="S26" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="T26" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="U26" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="V26" t="str">
+        <v>10.00</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v>13245</v>
+      </c>
+      <c r="B27" t="str">
+        <v>انس سمير صالح محمد احمد</v>
+      </c>
+      <c r="C27" t="str">
+        <v>ثالث 1</v>
+      </c>
+      <c r="D27" t="str">
+        <v/>
+      </c>
+      <c r="E27" t="str">
+        <v/>
+      </c>
+      <c r="F27" t="str">
+        <v/>
+      </c>
+      <c r="G27" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="H27" t="str">
+        <v/>
+      </c>
+      <c r="I27" t="str">
+        <v/>
+      </c>
+      <c r="J27" t="str">
+        <v/>
+      </c>
+      <c r="K27" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27">
+        <v>0</v>
+      </c>
+      <c r="O27" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="P27" t="str">
+        <v/>
+      </c>
+      <c r="Q27" t="str">
+        <v/>
+      </c>
+      <c r="R27" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="S27" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="T27" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="U27" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="V27" t="str">
+        <v>10.00</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>30316</v>
+      </c>
+      <c r="B28" t="str">
+        <v>أنس شريف فوزي عبدالموجود</v>
+      </c>
+      <c r="C28" t="str">
+        <v>ثالث 1</v>
+      </c>
+      <c r="D28" t="str">
+        <v/>
+      </c>
+      <c r="E28" t="str">
+        <v/>
+      </c>
+      <c r="F28" t="str">
+        <v/>
+      </c>
+      <c r="G28" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="H28" t="str">
+        <v/>
+      </c>
+      <c r="I28" t="str">
+        <v/>
+      </c>
+      <c r="J28" t="str">
+        <v/>
+      </c>
+      <c r="K28" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28">
+        <v>0</v>
+      </c>
+      <c r="O28" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="P28" t="str">
+        <v/>
+      </c>
+      <c r="Q28" t="str">
+        <v/>
+      </c>
+      <c r="R28" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="S28" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="T28" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="U28" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="V28" t="str">
+        <v>10.00</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>28039</v>
+      </c>
+      <c r="B29" t="str">
+        <v>أنس صالح سنان المولد</v>
+      </c>
+      <c r="C29" t="str">
+        <v>ثالث 1</v>
+      </c>
+      <c r="D29" t="str">
+        <v/>
+      </c>
+      <c r="E29" t="str">
+        <v/>
+      </c>
+      <c r="F29" t="str">
+        <v/>
+      </c>
+      <c r="G29" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="H29" t="str">
+        <v/>
+      </c>
+      <c r="I29" t="str">
+        <v/>
+      </c>
+      <c r="J29" t="str">
+        <v/>
+      </c>
+      <c r="K29" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="L29">
+        <v>0</v>
+      </c>
+      <c r="M29">
+        <v>0</v>
+      </c>
+      <c r="N29">
+        <v>0</v>
+      </c>
+      <c r="O29" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="P29" t="str">
+        <v/>
+      </c>
+      <c r="Q29" t="str">
+        <v/>
+      </c>
+      <c r="R29" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="S29" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="T29" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="U29" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="V29" t="str">
+        <v>10.00</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>36607</v>
+      </c>
+      <c r="B30" t="str">
+        <v>انس محمد عبده الدوكري</v>
+      </c>
+      <c r="C30" t="str">
+        <v>ثالث 1</v>
+      </c>
+      <c r="D30" t="str">
+        <v/>
+      </c>
+      <c r="E30" t="str">
+        <v/>
+      </c>
+      <c r="F30" t="str">
+        <v/>
+      </c>
+      <c r="G30" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="H30" t="str">
+        <v/>
+      </c>
+      <c r="I30" t="str">
+        <v/>
+      </c>
+      <c r="J30" t="str">
+        <v/>
+      </c>
+      <c r="K30" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="L30">
+        <v>0</v>
+      </c>
+      <c r="M30">
+        <v>0</v>
+      </c>
+      <c r="N30">
+        <v>0</v>
+      </c>
+      <c r="O30" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="P30" t="str">
+        <v/>
+      </c>
+      <c r="Q30" t="str">
+        <v/>
+      </c>
+      <c r="R30" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="S30" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="T30" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="U30" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="V30" t="str">
+        <v>10.00</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>36865</v>
+      </c>
+      <c r="B31" t="str">
+        <v>اياد يوسف بن غالب الرفيعي</v>
+      </c>
+      <c r="C31" t="str">
+        <v>ثالث 1</v>
+      </c>
+      <c r="D31" t="str">
+        <v/>
+      </c>
+      <c r="E31" t="str">
+        <v/>
+      </c>
+      <c r="F31" t="str">
+        <v/>
+      </c>
+      <c r="G31" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="H31" t="str">
+        <v/>
+      </c>
+      <c r="I31" t="str">
+        <v/>
+      </c>
+      <c r="J31" t="str">
+        <v/>
+      </c>
+      <c r="K31" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="L31">
+        <v>0</v>
+      </c>
+      <c r="M31">
+        <v>0</v>
+      </c>
+      <c r="N31">
+        <v>0</v>
+      </c>
+      <c r="O31" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="P31" t="str">
+        <v/>
+      </c>
+      <c r="Q31" t="str">
+        <v/>
+      </c>
+      <c r="R31" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="S31" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="T31" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="U31" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="V31" t="str">
+        <v>10.00</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>09105</v>
+      </c>
+      <c r="B32" t="str">
+        <v>تركي محمد عياده الأحمدي</v>
+      </c>
+      <c r="C32" t="str">
+        <v>ثالث 1</v>
+      </c>
+      <c r="D32" t="str">
+        <v/>
+      </c>
+      <c r="E32" t="str">
+        <v/>
+      </c>
+      <c r="F32" t="str">
+        <v/>
+      </c>
+      <c r="G32" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="H32" t="str">
+        <v/>
+      </c>
+      <c r="I32" t="str">
+        <v/>
+      </c>
+      <c r="J32" t="str">
+        <v/>
+      </c>
+      <c r="K32" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="L32">
+        <v>0</v>
+      </c>
+      <c r="M32">
+        <v>0</v>
+      </c>
+      <c r="N32">
+        <v>0</v>
+      </c>
+      <c r="O32" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="P32" t="str">
+        <v/>
+      </c>
+      <c r="Q32" t="str">
+        <v/>
+      </c>
+      <c r="R32" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="S32" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="T32" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="U32" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="V32" t="str">
+        <v>10.00</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>93230</v>
+      </c>
+      <c r="B33" t="str">
+        <v>توفيق ضرار توفيق الحسين</v>
+      </c>
+      <c r="C33" t="str">
+        <v>ثالث 1</v>
+      </c>
+      <c r="D33" t="str">
+        <v/>
+      </c>
+      <c r="E33" t="str">
+        <v/>
+      </c>
+      <c r="F33" t="str">
+        <v/>
+      </c>
+      <c r="G33" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="H33" t="str">
+        <v/>
+      </c>
+      <c r="I33" t="str">
+        <v/>
+      </c>
+      <c r="J33" t="str">
+        <v/>
+      </c>
+      <c r="K33" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="L33">
+        <v>0</v>
+      </c>
+      <c r="M33">
+        <v>0</v>
+      </c>
+      <c r="N33">
+        <v>0</v>
+      </c>
+      <c r="O33" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="P33" t="str">
+        <v/>
+      </c>
+      <c r="Q33" t="str">
+        <v/>
+      </c>
+      <c r="R33" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="S33" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="T33" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="U33" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="V33" t="str">
+        <v>10.00</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>12401</v>
+      </c>
+      <c r="B34" t="str">
+        <v>تيم ساجد فائز قرة محمد</v>
+      </c>
+      <c r="C34" t="str">
+        <v>ثالث 1</v>
+      </c>
+      <c r="D34" t="str">
+        <v/>
+      </c>
+      <c r="E34" t="str">
+        <v/>
+      </c>
+      <c r="F34" t="str">
+        <v/>
+      </c>
+      <c r="G34" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="H34" t="str">
+        <v/>
+      </c>
+      <c r="I34" t="str">
+        <v/>
+      </c>
+      <c r="J34" t="str">
+        <v/>
+      </c>
+      <c r="K34" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="O34" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="P34" t="str">
+        <v/>
+      </c>
+      <c r="Q34" t="str">
+        <v/>
+      </c>
+      <c r="R34" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="S34" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="T34" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="U34" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="V34" t="str">
+        <v>10.00</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>96315</v>
+      </c>
+      <c r="B35" t="str">
+        <v>جسار وسام سعيد الزراري</v>
+      </c>
+      <c r="C35" t="str">
+        <v>ثالث 1</v>
+      </c>
+      <c r="D35" t="str">
+        <v/>
+      </c>
+      <c r="E35" t="str">
+        <v/>
+      </c>
+      <c r="F35" t="str">
+        <v/>
+      </c>
+      <c r="G35" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="H35" t="str">
+        <v/>
+      </c>
+      <c r="I35" t="str">
+        <v/>
+      </c>
+      <c r="J35" t="str">
+        <v/>
+      </c>
+      <c r="K35" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="L35">
+        <v>0</v>
+      </c>
+      <c r="M35">
+        <v>0</v>
+      </c>
+      <c r="N35">
+        <v>0</v>
+      </c>
+      <c r="O35" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="P35" t="str">
+        <v/>
+      </c>
+      <c r="Q35" t="str">
+        <v/>
+      </c>
+      <c r="R35" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="S35" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="T35" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="U35" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="V35" t="str">
+        <v>10.00</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>22072</v>
+      </c>
+      <c r="B36" t="str">
+        <v>حاتم عبد المنعم محمد عباس</v>
+      </c>
+      <c r="C36" t="str">
+        <v>ثالث 1</v>
+      </c>
+      <c r="D36" t="str">
+        <v/>
+      </c>
+      <c r="E36" t="str">
+        <v/>
+      </c>
+      <c r="F36" t="str">
+        <v/>
+      </c>
+      <c r="G36" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="H36" t="str">
+        <v/>
+      </c>
+      <c r="I36" t="str">
+        <v/>
+      </c>
+      <c r="J36" t="str">
+        <v/>
+      </c>
+      <c r="K36" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="O36" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="P36" t="str">
+        <v/>
+      </c>
+      <c r="Q36" t="str">
+        <v/>
+      </c>
+      <c r="R36" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="S36" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="T36" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="U36" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="V36" t="str">
+        <v>10.00</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>00756</v>
+      </c>
+      <c r="B37" t="str">
+        <v>ريان محمد حميد الفقيه</v>
+      </c>
+      <c r="C37" t="str">
+        <v>ثالث 1</v>
+      </c>
+      <c r="D37" t="str">
+        <v/>
+      </c>
+      <c r="E37" t="str">
+        <v/>
+      </c>
+      <c r="F37" t="str">
+        <v/>
+      </c>
+      <c r="G37" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="H37" t="str">
+        <v/>
+      </c>
+      <c r="I37" t="str">
+        <v/>
+      </c>
+      <c r="J37" t="str">
+        <v/>
+      </c>
+      <c r="K37" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="N37">
+        <v>0</v>
+      </c>
+      <c r="O37" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="P37" t="str">
+        <v/>
+      </c>
+      <c r="Q37" t="str">
+        <v/>
+      </c>
+      <c r="R37" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="S37" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="T37" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="U37" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="V37" t="str">
+        <v>10.00</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>37119</v>
+      </c>
+      <c r="B38" t="str">
+        <v>سامي طالب مسلم الجهني</v>
+      </c>
+      <c r="C38" t="str">
+        <v>ثالث 1</v>
+      </c>
+      <c r="D38" t="str">
+        <v/>
+      </c>
+      <c r="E38" t="str">
+        <v/>
+      </c>
+      <c r="F38" t="str">
+        <v/>
+      </c>
+      <c r="G38" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="H38" t="str">
+        <v/>
+      </c>
+      <c r="I38" t="str">
+        <v/>
+      </c>
+      <c r="J38" t="str">
+        <v/>
+      </c>
+      <c r="K38" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38">
+        <v>0</v>
+      </c>
+      <c r="N38">
+        <v>0</v>
+      </c>
+      <c r="O38" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="P38" t="str">
+        <v/>
+      </c>
+      <c r="Q38" t="str">
+        <v/>
+      </c>
+      <c r="R38" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="S38" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="T38" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="U38" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="V38" t="str">
+        <v>10.00</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>72861</v>
+      </c>
+      <c r="B39" t="str">
+        <v>عبدالرحمن فيصل علي الأحمدي</v>
+      </c>
+      <c r="C39" t="str">
+        <v>ثالث 1</v>
+      </c>
+      <c r="D39" t="str">
+        <v/>
+      </c>
+      <c r="E39" t="str">
+        <v/>
+      </c>
+      <c r="F39" t="str">
+        <v/>
+      </c>
+      <c r="G39" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="H39" t="str">
+        <v/>
+      </c>
+      <c r="I39" t="str">
+        <v/>
+      </c>
+      <c r="J39" t="str">
+        <v/>
+      </c>
+      <c r="K39" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39">
+        <v>0</v>
+      </c>
+      <c r="O39" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="P39" t="str">
+        <v/>
+      </c>
+      <c r="Q39" t="str">
+        <v/>
+      </c>
+      <c r="R39" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="S39" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="T39" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="U39" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="V39" t="str">
+        <v>10.00</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>44201</v>
+      </c>
+      <c r="B40" t="str">
+        <v>عبدالرحمن محمد أحمد البدري</v>
+      </c>
+      <c r="C40" t="str">
+        <v>ثالث 1</v>
+      </c>
+      <c r="D40" t="str">
+        <v/>
+      </c>
+      <c r="E40" t="str">
+        <v/>
+      </c>
+      <c r="F40" t="str">
+        <v/>
+      </c>
+      <c r="G40" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="H40" t="str">
+        <v/>
+      </c>
+      <c r="I40" t="str">
+        <v/>
+      </c>
+      <c r="J40" t="str">
+        <v/>
+      </c>
+      <c r="K40" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="N40">
+        <v>0</v>
+      </c>
+      <c r="O40" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="P40" t="str">
+        <v/>
+      </c>
+      <c r="Q40" t="str">
+        <v/>
+      </c>
+      <c r="R40" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="S40" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="T40" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="U40" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="V40" t="str">
+        <v>10.00</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>44445</v>
+      </c>
+      <c r="B41" t="str">
+        <v>عبدالله</v>
+      </c>
+      <c r="C41" t="str">
+        <v>ثالث 2</v>
+      </c>
+      <c r="D41" t="str">
+        <v/>
+      </c>
+      <c r="E41" t="str">
+        <v/>
+      </c>
+      <c r="F41" t="str">
+        <v/>
+      </c>
+      <c r="G41" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="H41" t="str">
+        <v/>
+      </c>
+      <c r="I41" t="str">
+        <v/>
+      </c>
+      <c r="J41" t="str">
+        <v/>
+      </c>
+      <c r="K41" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+      <c r="N41">
+        <v>0</v>
+      </c>
+      <c r="O41" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="P41" t="str">
+        <v/>
+      </c>
+      <c r="Q41" t="str">
+        <v/>
+      </c>
+      <c r="R41" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="S41" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="T41" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="U41" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="V41" t="str">
+        <v>10.00</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>33333</v>
+      </c>
+      <c r="B42" t="str">
+        <v>عبدالملك</v>
+      </c>
+      <c r="C42" t="str">
+        <v>ثالث 2</v>
+      </c>
+      <c r="D42" t="str">
+        <v/>
+      </c>
+      <c r="E42" t="str">
+        <v/>
+      </c>
+      <c r="F42" t="str">
+        <v/>
+      </c>
+      <c r="G42" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="H42" t="str">
+        <v/>
+      </c>
+      <c r="I42" t="str">
+        <v/>
+      </c>
+      <c r="J42" t="str">
+        <v/>
+      </c>
+      <c r="K42" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42">
+        <v>0</v>
+      </c>
+      <c r="N42">
+        <v>0</v>
+      </c>
+      <c r="O42" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="P42" t="str">
+        <v/>
+      </c>
+      <c r="Q42" t="str">
+        <v/>
+      </c>
+      <c r="R42" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="S42" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="T42" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="U42" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="V42" t="str">
+        <v>10.00</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>34387</v>
+      </c>
+      <c r="B43" t="str">
+        <v>عمر عبدالرحمن بن يحيى سيدي بابا</v>
+      </c>
+      <c r="C43" t="str">
+        <v>ثالث 1</v>
+      </c>
+      <c r="D43" t="str">
+        <v/>
+      </c>
+      <c r="E43" t="str">
+        <v/>
+      </c>
+      <c r="F43" t="str">
+        <v/>
+      </c>
+      <c r="G43" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="H43" t="str">
+        <v/>
+      </c>
+      <c r="I43" t="str">
+        <v/>
+      </c>
+      <c r="J43" t="str">
+        <v/>
+      </c>
+      <c r="K43" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43">
+        <v>0</v>
+      </c>
+      <c r="N43">
+        <v>0</v>
+      </c>
+      <c r="O43" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="P43" t="str">
+        <v/>
+      </c>
+      <c r="Q43" t="str">
+        <v/>
+      </c>
+      <c r="R43" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="S43" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="T43" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="U43" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="V43" t="str">
+        <v>10.00</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>55201</v>
+      </c>
+      <c r="B44" t="str">
+        <v>محمد حمزة محمود سليمان</v>
+      </c>
+      <c r="C44" t="str">
+        <v>ثالث 1</v>
+      </c>
+      <c r="D44" t="str">
+        <v/>
+      </c>
+      <c r="E44" t="str">
+        <v/>
+      </c>
+      <c r="F44" t="str">
+        <v/>
+      </c>
+      <c r="G44" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="H44" t="str">
+        <v/>
+      </c>
+      <c r="I44" t="str">
+        <v/>
+      </c>
+      <c r="J44" t="str">
+        <v/>
+      </c>
+      <c r="K44" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44">
+        <v>0</v>
+      </c>
+      <c r="N44">
+        <v>0</v>
+      </c>
+      <c r="O44" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="P44" t="str">
+        <v/>
+      </c>
+      <c r="Q44" t="str">
+        <v/>
+      </c>
+      <c r="R44" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="S44" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="T44" t="str">
+        <v>10.00</v>
+      </c>
+      <c r="U44" t="str">
+        <v>0.00</v>
+      </c>
+      <c r="V44" t="str">
+        <v>10.00</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:V44"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:H44"/>
   <sheetData>
     <row r="1">
@@ -10240,19 +13244,19 @@
         <v>ثالث 1</v>
       </c>
       <c r="D2" t="str">
-        <v>1.94</v>
+        <v>1.46</v>
       </c>
       <c r="E2" t="str">
-        <v>1.11</v>
+        <v>0.83</v>
       </c>
       <c r="F2" t="str">
         <v>10.00</v>
       </c>
       <c r="G2" t="str">
-        <v>6.67</v>
+        <v>5.00</v>
       </c>
       <c r="H2" t="str">
-        <v>19.72</v>
+        <v>17.29</v>
       </c>
     </row>
     <row r="3">
@@ -10266,7 +13270,7 @@
         <v>ثالث 1</v>
       </c>
       <c r="D3" t="str">
-        <v>1.33</v>
+        <v>1.00</v>
       </c>
       <c r="E3" t="str">
         <v>0.00</v>
@@ -10278,7 +13282,7 @@
         <v>0.00</v>
       </c>
       <c r="H3" t="str">
-        <v>11.33</v>
+        <v>11.00</v>
       </c>
     </row>
     <row r="4">
@@ -10292,7 +13296,7 @@
         <v>ثالث 1</v>
       </c>
       <c r="D4" t="str">
-        <v>1.11</v>
+        <v>0.83</v>
       </c>
       <c r="E4" t="str">
         <v>0.00</v>
@@ -10304,7 +13308,7 @@
         <v>0.00</v>
       </c>
       <c r="H4" t="str">
-        <v>11.11</v>
+        <v>10.83</v>
       </c>
     </row>
     <row r="5">
@@ -10318,7 +13322,7 @@
         <v>ثالث 1</v>
       </c>
       <c r="D5" t="str">
-        <v>1.11</v>
+        <v>0.83</v>
       </c>
       <c r="E5" t="str">
         <v>0.00</v>
@@ -10330,7 +13334,7 @@
         <v>0.00</v>
       </c>
       <c r="H5" t="str">
-        <v>11.11</v>
+        <v>10.83</v>
       </c>
     </row>
     <row r="6">
@@ -10344,10 +13348,10 @@
         <v>ثالث 1</v>
       </c>
       <c r="D6" t="str">
-        <v>2.67</v>
+        <v>2.00</v>
       </c>
       <c r="E6" t="str">
-        <v>2.00</v>
+        <v>1.50</v>
       </c>
       <c r="F6" t="str">
         <v>10.00</v>
@@ -10356,7 +13360,7 @@
         <v>0.00</v>
       </c>
       <c r="H6" t="str">
-        <v>14.67</v>
+        <v>13.50</v>
       </c>
     </row>
     <row r="7">
@@ -10370,7 +13374,7 @@
         <v>ثالث 1</v>
       </c>
       <c r="D7" t="str">
-        <v>0.67</v>
+        <v>0.50</v>
       </c>
       <c r="E7" t="str">
         <v>0.00</v>
@@ -10382,7 +13386,7 @@
         <v>0.00</v>
       </c>
       <c r="H7" t="str">
-        <v>10.67</v>
+        <v>10.50</v>
       </c>
     </row>
     <row r="8">
@@ -10451,7 +13455,7 @@
         <v>0.00</v>
       </c>
       <c r="E10" t="str">
-        <v>2.00</v>
+        <v>1.50</v>
       </c>
       <c r="F10" t="str">
         <v>10.00</v>
@@ -10460,7 +13464,7 @@
         <v>0.00</v>
       </c>
       <c r="H10" t="str">
-        <v>12.00</v>
+        <v>11.50</v>
       </c>
     </row>
     <row r="11">
@@ -10604,19 +13608,19 @@
         <v>ثالث 1</v>
       </c>
       <c r="D16" t="str">
-        <v>5.67</v>
+        <v>4.75</v>
       </c>
       <c r="E16" t="str">
-        <v>10.60</v>
+        <v>9.95</v>
       </c>
       <c r="F16" t="str">
-        <v>9.50</v>
+        <v>9.63</v>
       </c>
       <c r="G16" t="str">
-        <v>14.67</v>
+        <v>14.75</v>
       </c>
       <c r="H16" t="str">
-        <v>40.43</v>
+        <v>39.08</v>
       </c>
     </row>
     <row r="17">
